--- a/plan/plan.xlsx
+++ b/plan/plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Documents\nas_copy\homes\Docgui\Reconversion\BPREA\06 - Planif GIT\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A8AD4E-47F8-4A00-895D-D77E947ECA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CB8B1E-5D86-4E76-A7BB-BF810B62B8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24660" windowHeight="14445" activeTab="4" xr2:uid="{16ADF3EB-A2C6-4F07-8557-221D48410A7D}"/>
+    <workbookView xWindow="28680" yWindow="630" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{16ADF3EB-A2C6-4F07-8557-221D48410A7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil3 (3)" sheetId="5" r:id="rId1"/>
@@ -805,6 +805,231 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="15" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -940,231 +1165,6 @@
     <xf numFmtId="18" fontId="10" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="15" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="16" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1222,6 +1222,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1240,6 +1249,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1249,20 +1264,182 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="7" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1273,24 +1450,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1316,165 +1475,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="7" fillId="11" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1798,55 +1798,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B34A5D12-ED35-4757-8EB1-96698A84E938}">
   <dimension ref="B2:BP85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="3" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="3.6640625" customWidth="1"/>
-    <col min="23" max="23" width="4.6640625" customWidth="1"/>
-    <col min="24" max="24" width="5.6640625" customWidth="1"/>
-    <col min="25" max="26" width="4.6640625" customWidth="1"/>
-    <col min="27" max="27" width="5.6640625" customWidth="1"/>
-    <col min="28" max="29" width="4.6640625" customWidth="1"/>
-    <col min="30" max="30" width="5.88671875" customWidth="1"/>
-    <col min="31" max="33" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="3.7109375" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" customWidth="1"/>
+    <col min="25" max="26" width="4.7109375" customWidth="1"/>
+    <col min="27" max="27" width="5.7109375" customWidth="1"/>
+    <col min="28" max="29" width="4.7109375" customWidth="1"/>
+    <col min="30" max="30" width="5.85546875" customWidth="1"/>
+    <col min="31" max="33" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="D2" s="128" t="s">
+    <row r="2" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="D2" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="129"/>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="129"/>
-      <c r="R2" s="129"/>
-      <c r="S2" s="129"/>
-      <c r="T2" s="129"/>
-      <c r="U2" s="129"/>
-      <c r="V2" s="129"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="129"/>
-      <c r="Y2" s="129"/>
-      <c r="Z2" s="129"/>
-      <c r="AA2" s="129"/>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="129"/>
-      <c r="AD2" s="129"/>
-      <c r="AE2" s="130"/>
-    </row>
-    <row r="4" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B4" s="131" t="s">
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="105"/>
+      <c r="M2" s="105"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="105"/>
+      <c r="U2" s="105"/>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
+      <c r="Y2" s="105"/>
+      <c r="Z2" s="105"/>
+      <c r="AA2" s="105"/>
+      <c r="AB2" s="105"/>
+      <c r="AC2" s="105"/>
+      <c r="AD2" s="105"/>
+      <c r="AE2" s="106"/>
+    </row>
+    <row r="4" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="41" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="17"/>
@@ -1878,185 +1878,185 @@
       <c r="AD4" s="32"/>
       <c r="AE4" s="19"/>
     </row>
-    <row r="5" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="132"/>
+    <row r="5" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="42"/>
       <c r="D5" s="20"/>
-      <c r="E5" s="134" t="s">
+      <c r="E5" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="136"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="46"/>
       <c r="L5" s="31"/>
-      <c r="M5" s="134" t="s">
+      <c r="M5" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="N5" s="135"/>
-      <c r="O5" s="135"/>
-      <c r="P5" s="135"/>
-      <c r="Q5" s="135"/>
-      <c r="R5" s="135"/>
-      <c r="S5" s="136"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
+      <c r="P5" s="45"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="45"/>
+      <c r="S5" s="46"/>
       <c r="T5" s="21"/>
       <c r="U5" s="21"/>
       <c r="V5" s="33"/>
       <c r="W5" s="33"/>
-      <c r="X5" s="143" t="s">
+      <c r="X5" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="144"/>
-      <c r="Z5" s="144"/>
-      <c r="AA5" s="144"/>
-      <c r="AB5" s="144"/>
-      <c r="AC5" s="144"/>
-      <c r="AD5" s="145"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="54"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="54"/>
+      <c r="AD5" s="55"/>
       <c r="AE5" s="22"/>
     </row>
-    <row r="6" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="132"/>
+    <row r="6" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="42"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="139"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="49"/>
       <c r="L6" s="31"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="138"/>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
-      <c r="S6" s="139"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="49"/>
       <c r="T6" s="21"/>
       <c r="U6" s="21"/>
       <c r="V6" s="33"/>
       <c r="W6" s="33"/>
-      <c r="X6" s="146"/>
-      <c r="Y6" s="147"/>
-      <c r="Z6" s="147"/>
-      <c r="AA6" s="147"/>
-      <c r="AB6" s="147"/>
-      <c r="AC6" s="147"/>
-      <c r="AD6" s="148"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="57"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="57"/>
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="58"/>
       <c r="AE6" s="22"/>
     </row>
-    <row r="7" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="132"/>
+    <row r="7" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="42"/>
       <c r="D7" s="20"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="138"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="138"/>
-      <c r="I7" s="138"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="139"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="49"/>
       <c r="L7" s="31"/>
-      <c r="M7" s="137"/>
-      <c r="N7" s="138"/>
-      <c r="O7" s="138"/>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
-      <c r="S7" s="139"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="49"/>
       <c r="T7" s="21"/>
       <c r="U7" s="21"/>
       <c r="V7" s="33"/>
       <c r="W7" s="33"/>
-      <c r="X7" s="146"/>
-      <c r="Y7" s="147"/>
-      <c r="Z7" s="147"/>
-      <c r="AA7" s="147"/>
-      <c r="AB7" s="147"/>
-      <c r="AC7" s="147"/>
-      <c r="AD7" s="148"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="57"/>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="57"/>
+      <c r="AB7" s="57"/>
+      <c r="AC7" s="57"/>
+      <c r="AD7" s="58"/>
       <c r="AE7" s="22"/>
     </row>
-    <row r="8" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="132"/>
+    <row r="8" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="42"/>
       <c r="D8" s="20"/>
-      <c r="E8" s="137"/>
-      <c r="F8" s="138"/>
-      <c r="G8" s="138"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="138"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="139"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="49"/>
       <c r="L8" s="31"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="138"/>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
-      <c r="S8" s="139"/>
+      <c r="M8" s="47"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="49"/>
       <c r="T8" s="21"/>
       <c r="U8" s="21"/>
       <c r="V8" s="33"/>
       <c r="W8" s="33"/>
-      <c r="X8" s="146"/>
-      <c r="Y8" s="147"/>
-      <c r="Z8" s="147"/>
-      <c r="AA8" s="147"/>
-      <c r="AB8" s="147"/>
-      <c r="AC8" s="147"/>
-      <c r="AD8" s="148"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
+      <c r="AA8" s="57"/>
+      <c r="AB8" s="57"/>
+      <c r="AC8" s="57"/>
+      <c r="AD8" s="58"/>
       <c r="AE8" s="22"/>
     </row>
-    <row r="9" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="132"/>
+    <row r="9" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="42"/>
       <c r="D9" s="20"/>
-      <c r="E9" s="137"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
-      <c r="I9" s="138"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="139"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="49"/>
       <c r="L9" s="31"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="138"/>
-      <c r="O9" s="138"/>
-      <c r="P9" s="138"/>
-      <c r="Q9" s="138"/>
-      <c r="R9" s="138"/>
-      <c r="S9" s="139"/>
+      <c r="M9" s="47"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="49"/>
       <c r="T9" s="21"/>
       <c r="U9" s="21"/>
       <c r="V9" s="33"/>
       <c r="W9" s="33"/>
-      <c r="X9" s="149"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="151"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="61"/>
       <c r="AE9" s="22"/>
     </row>
-    <row r="10" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="132"/>
+    <row r="10" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="42"/>
       <c r="D10" s="20"/>
-      <c r="E10" s="137"/>
-      <c r="F10" s="138"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="139"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="49"/>
       <c r="L10" s="31"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="138"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="138"/>
-      <c r="R10" s="138"/>
-      <c r="S10" s="139"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="49"/>
       <c r="T10" s="21"/>
       <c r="U10" s="21"/>
       <c r="V10" s="33"/>
@@ -2070,24 +2070,24 @@
       <c r="AD10" s="33"/>
       <c r="AE10" s="22"/>
     </row>
-    <row r="11" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="132"/>
+    <row r="11" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="42"/>
       <c r="D11" s="20"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="142"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="52"/>
       <c r="L11" s="31"/>
-      <c r="M11" s="140"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="141"/>
-      <c r="P11" s="141"/>
-      <c r="Q11" s="141"/>
-      <c r="R11" s="141"/>
-      <c r="S11" s="142"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="52"/>
       <c r="T11" s="21"/>
       <c r="U11" s="21"/>
       <c r="V11" s="33"/>
@@ -2101,8 +2101,8 @@
       <c r="AD11" s="33"/>
       <c r="AE11" s="22"/>
     </row>
-    <row r="12" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="132"/>
+    <row r="12" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="42"/>
       <c r="D12" s="20"/>
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
@@ -2122,230 +2122,230 @@
       <c r="T12" s="21"/>
       <c r="U12" s="21"/>
       <c r="V12" s="33"/>
-      <c r="W12" s="86" t="s">
+      <c r="W12" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="X12" s="87"/>
+      <c r="X12" s="63"/>
       <c r="Y12" s="33"/>
-      <c r="Z12" s="86" t="s">
+      <c r="Z12" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AA12" s="87"/>
+      <c r="AA12" s="63"/>
       <c r="AB12" s="33"/>
-      <c r="AC12" s="86" t="s">
+      <c r="AC12" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AD12" s="87"/>
+      <c r="AD12" s="63"/>
       <c r="AE12" s="22"/>
     </row>
-    <row r="13" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="132"/>
+    <row r="13" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="42"/>
       <c r="D13" s="20"/>
-      <c r="E13" s="152" t="s">
+      <c r="E13" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="153"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="154"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
       <c r="L13" s="31"/>
-      <c r="M13" s="92" t="s">
+      <c r="M13" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="94"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="79"/>
       <c r="T13" s="21"/>
       <c r="U13" s="21"/>
       <c r="V13" s="33"/>
-      <c r="W13" s="88"/>
-      <c r="X13" s="89"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="65"/>
       <c r="Y13" s="33"/>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="89"/>
+      <c r="Z13" s="64"/>
+      <c r="AA13" s="65"/>
       <c r="AB13" s="33"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="89"/>
+      <c r="AC13" s="64"/>
+      <c r="AD13" s="65"/>
       <c r="AE13" s="22"/>
     </row>
-    <row r="14" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="132"/>
+    <row r="14" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="42"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="155"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="156"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="157"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="73"/>
       <c r="L14" s="31"/>
-      <c r="M14" s="95"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="97"/>
+      <c r="M14" s="80"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="82"/>
       <c r="T14" s="21"/>
       <c r="U14" s="21"/>
       <c r="V14" s="33"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="89"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="65"/>
       <c r="Y14" s="33"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="89"/>
+      <c r="Z14" s="64"/>
+      <c r="AA14" s="65"/>
       <c r="AB14" s="33"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="89"/>
+      <c r="AC14" s="64"/>
+      <c r="AD14" s="65"/>
       <c r="AE14" s="22"/>
     </row>
-    <row r="15" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="132"/>
+    <row r="15" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="42"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="155"/>
-      <c r="F15" s="156"/>
-      <c r="G15" s="156"/>
-      <c r="H15" s="156"/>
-      <c r="I15" s="156"/>
-      <c r="J15" s="156"/>
-      <c r="K15" s="157"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="73"/>
       <c r="L15" s="31"/>
-      <c r="M15" s="95"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
-      <c r="S15" s="97"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="82"/>
       <c r="T15" s="21"/>
       <c r="U15" s="21"/>
       <c r="V15" s="33"/>
-      <c r="W15" s="88"/>
-      <c r="X15" s="89"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="65"/>
       <c r="Y15" s="33"/>
-      <c r="Z15" s="88"/>
-      <c r="AA15" s="89"/>
+      <c r="Z15" s="64"/>
+      <c r="AA15" s="65"/>
       <c r="AB15" s="33"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="89"/>
+      <c r="AC15" s="64"/>
+      <c r="AD15" s="65"/>
       <c r="AE15" s="22"/>
     </row>
-    <row r="16" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="132"/>
+    <row r="16" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="42"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="155"/>
-      <c r="F16" s="156"/>
-      <c r="G16" s="156"/>
-      <c r="H16" s="156"/>
-      <c r="I16" s="156"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="157"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="73"/>
       <c r="L16" s="31"/>
-      <c r="M16" s="95"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="96"/>
-      <c r="P16" s="96"/>
-      <c r="Q16" s="96"/>
-      <c r="R16" s="96"/>
-      <c r="S16" s="97"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="82"/>
       <c r="T16" s="21"/>
       <c r="U16" s="21"/>
       <c r="V16" s="33"/>
-      <c r="W16" s="88"/>
-      <c r="X16" s="89"/>
+      <c r="W16" s="64"/>
+      <c r="X16" s="65"/>
       <c r="Y16" s="33"/>
-      <c r="Z16" s="88"/>
-      <c r="AA16" s="89"/>
+      <c r="Z16" s="64"/>
+      <c r="AA16" s="65"/>
       <c r="AB16" s="33"/>
-      <c r="AC16" s="88"/>
-      <c r="AD16" s="89"/>
+      <c r="AC16" s="64"/>
+      <c r="AD16" s="65"/>
       <c r="AE16" s="22"/>
     </row>
-    <row r="17" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="132"/>
+    <row r="17" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="42"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="155"/>
-      <c r="F17" s="156"/>
-      <c r="G17" s="156"/>
-      <c r="H17" s="156"/>
-      <c r="I17" s="156"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="157"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="73"/>
       <c r="L17" s="31"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="96"/>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="97"/>
+      <c r="M17" s="80"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="82"/>
       <c r="T17" s="21"/>
       <c r="U17" s="21"/>
       <c r="V17" s="33"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="89"/>
+      <c r="W17" s="64"/>
+      <c r="X17" s="65"/>
       <c r="Y17" s="33"/>
-      <c r="Z17" s="88"/>
-      <c r="AA17" s="89"/>
+      <c r="Z17" s="64"/>
+      <c r="AA17" s="65"/>
       <c r="AB17" s="33"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="89"/>
+      <c r="AC17" s="64"/>
+      <c r="AD17" s="65"/>
       <c r="AE17" s="22"/>
     </row>
-    <row r="18" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="132"/>
+    <row r="18" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="42"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="156"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="156"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="156"/>
-      <c r="K18" s="157"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="73"/>
       <c r="L18" s="31"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="96"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="96"/>
-      <c r="S18" s="97"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="82"/>
       <c r="T18" s="21"/>
       <c r="U18" s="21"/>
       <c r="V18" s="33"/>
-      <c r="W18" s="90"/>
-      <c r="X18" s="91"/>
+      <c r="W18" s="66"/>
+      <c r="X18" s="67"/>
       <c r="Y18" s="33"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="91"/>
+      <c r="Z18" s="66"/>
+      <c r="AA18" s="67"/>
       <c r="AB18" s="33"/>
-      <c r="AC18" s="90"/>
-      <c r="AD18" s="91"/>
+      <c r="AC18" s="66"/>
+      <c r="AD18" s="67"/>
       <c r="AE18" s="22"/>
     </row>
-    <row r="19" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="132"/>
+    <row r="19" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="42"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="159"/>
-      <c r="G19" s="159"/>
-      <c r="H19" s="159"/>
-      <c r="I19" s="159"/>
-      <c r="J19" s="159"/>
-      <c r="K19" s="160"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="76"/>
       <c r="L19" s="31"/>
-      <c r="M19" s="98"/>
-      <c r="N19" s="99"/>
-      <c r="O19" s="99"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="99"/>
-      <c r="S19" s="100"/>
+      <c r="M19" s="83"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="85"/>
       <c r="T19" s="21"/>
       <c r="U19" s="21"/>
       <c r="V19" s="33"/>
@@ -2360,8 +2360,8 @@
       <c r="AE19" s="22"/>
       <c r="AL19" s="25"/>
     </row>
-    <row r="20" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="132"/>
+    <row r="20" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="42"/>
       <c r="D20" s="20"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -2381,232 +2381,232 @@
       <c r="T20" s="21"/>
       <c r="U20" s="21"/>
       <c r="V20" s="33"/>
-      <c r="W20" s="86" t="s">
+      <c r="W20" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="X20" s="87"/>
+      <c r="X20" s="63"/>
       <c r="Y20" s="33"/>
-      <c r="Z20" s="86" t="s">
+      <c r="Z20" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AA20" s="87"/>
+      <c r="AA20" s="63"/>
       <c r="AB20" s="33"/>
-      <c r="AC20" s="86" t="s">
+      <c r="AC20" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AD20" s="87"/>
+      <c r="AD20" s="63"/>
       <c r="AE20" s="22"/>
       <c r="AN20" s="26"/>
     </row>
-    <row r="21" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="132"/>
+    <row r="21" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="42"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="92" t="s">
+      <c r="E21" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="93"/>
-      <c r="G21" s="93"/>
-      <c r="H21" s="93"/>
-      <c r="I21" s="93"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="94"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="79"/>
       <c r="L21" s="31"/>
-      <c r="M21" s="101" t="s">
+      <c r="M21" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="N21" s="102"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="102"/>
-      <c r="R21" s="102"/>
-      <c r="S21" s="103"/>
+      <c r="N21" s="108"/>
+      <c r="O21" s="108"/>
+      <c r="P21" s="108"/>
+      <c r="Q21" s="108"/>
+      <c r="R21" s="108"/>
+      <c r="S21" s="109"/>
       <c r="T21" s="21"/>
       <c r="U21" s="21"/>
       <c r="V21" s="33"/>
-      <c r="W21" s="88"/>
-      <c r="X21" s="89"/>
+      <c r="W21" s="64"/>
+      <c r="X21" s="65"/>
       <c r="Y21" s="33"/>
-      <c r="Z21" s="88"/>
-      <c r="AA21" s="89"/>
+      <c r="Z21" s="64"/>
+      <c r="AA21" s="65"/>
       <c r="AB21" s="33"/>
-      <c r="AC21" s="88"/>
-      <c r="AD21" s="89"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="65"/>
       <c r="AE21" s="22"/>
       <c r="AR21" s="28"/>
     </row>
-    <row r="22" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="132"/>
+    <row r="22" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="42"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="96"/>
-      <c r="I22" s="96"/>
-      <c r="J22" s="96"/>
-      <c r="K22" s="97"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="82"/>
       <c r="L22" s="31"/>
-      <c r="M22" s="104"/>
-      <c r="N22" s="105"/>
-      <c r="O22" s="105"/>
-      <c r="P22" s="105"/>
-      <c r="Q22" s="105"/>
-      <c r="R22" s="105"/>
-      <c r="S22" s="106"/>
+      <c r="M22" s="110"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="111"/>
+      <c r="S22" s="112"/>
       <c r="T22" s="21"/>
       <c r="U22" s="21"/>
       <c r="V22" s="33"/>
-      <c r="W22" s="88"/>
-      <c r="X22" s="89"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="65"/>
       <c r="Y22" s="33"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="89"/>
+      <c r="Z22" s="64"/>
+      <c r="AA22" s="65"/>
       <c r="AB22" s="33"/>
-      <c r="AC22" s="88"/>
-      <c r="AD22" s="89"/>
+      <c r="AC22" s="64"/>
+      <c r="AD22" s="65"/>
       <c r="AE22" s="22"/>
     </row>
-    <row r="23" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="132"/>
+    <row r="23" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="42"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="95"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="96"/>
-      <c r="I23" s="96"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="97"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="82"/>
       <c r="L23" s="31"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="105"/>
-      <c r="Q23" s="105"/>
-      <c r="R23" s="105"/>
-      <c r="S23" s="106"/>
+      <c r="M23" s="110"/>
+      <c r="N23" s="111"/>
+      <c r="O23" s="111"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="111"/>
+      <c r="S23" s="112"/>
       <c r="T23" s="21"/>
       <c r="U23" s="21"/>
       <c r="V23" s="33"/>
-      <c r="W23" s="88"/>
-      <c r="X23" s="89"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="65"/>
       <c r="Y23" s="33"/>
-      <c r="Z23" s="88"/>
-      <c r="AA23" s="89"/>
+      <c r="Z23" s="64"/>
+      <c r="AA23" s="65"/>
       <c r="AB23" s="33"/>
-      <c r="AC23" s="88"/>
-      <c r="AD23" s="89"/>
+      <c r="AC23" s="64"/>
+      <c r="AD23" s="65"/>
       <c r="AE23" s="22"/>
     </row>
-    <row r="24" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="132"/>
+    <row r="24" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="42"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
-      <c r="H24" s="96"/>
-      <c r="I24" s="96"/>
-      <c r="J24" s="96"/>
-      <c r="K24" s="97"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="82"/>
       <c r="L24" s="31"/>
-      <c r="M24" s="104"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
-      <c r="Q24" s="105"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="106"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="112"/>
       <c r="T24" s="21"/>
       <c r="U24" s="21"/>
       <c r="V24" s="33"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="89"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="65"/>
       <c r="Y24" s="33"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="89"/>
+      <c r="Z24" s="64"/>
+      <c r="AA24" s="65"/>
       <c r="AB24" s="33"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="89"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="65"/>
       <c r="AE24" s="22"/>
     </row>
-    <row r="25" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="132"/>
+    <row r="25" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="42"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="96"/>
-      <c r="G25" s="96"/>
-      <c r="H25" s="96"/>
-      <c r="I25" s="96"/>
-      <c r="J25" s="96"/>
-      <c r="K25" s="97"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="82"/>
       <c r="L25" s="31"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="105"/>
-      <c r="R25" s="105"/>
-      <c r="S25" s="106"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="112"/>
       <c r="T25" s="21"/>
       <c r="U25" s="21"/>
       <c r="V25" s="33"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="89"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="65"/>
       <c r="Y25" s="33"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="89"/>
+      <c r="Z25" s="64"/>
+      <c r="AA25" s="65"/>
       <c r="AB25" s="33"/>
-      <c r="AC25" s="88"/>
-      <c r="AD25" s="89"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="65"/>
       <c r="AE25" s="22"/>
     </row>
-    <row r="26" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="132"/>
+    <row r="26" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="42"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="96"/>
-      <c r="G26" s="96"/>
-      <c r="H26" s="96"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="97"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="82"/>
       <c r="L26" s="31"/>
-      <c r="M26" s="104"/>
-      <c r="N26" s="105"/>
-      <c r="O26" s="105"/>
-      <c r="P26" s="105"/>
-      <c r="Q26" s="105"/>
-      <c r="R26" s="105"/>
-      <c r="S26" s="106"/>
+      <c r="M26" s="110"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="111"/>
+      <c r="S26" s="112"/>
       <c r="T26" s="21"/>
       <c r="U26" s="21"/>
       <c r="V26" s="33"/>
-      <c r="W26" s="90"/>
-      <c r="X26" s="91"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="67"/>
       <c r="Y26" s="33"/>
-      <c r="Z26" s="90"/>
-      <c r="AA26" s="91"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="67"/>
       <c r="AB26" s="33"/>
-      <c r="AC26" s="90"/>
-      <c r="AD26" s="91"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="67"/>
       <c r="AE26" s="22"/>
     </row>
-    <row r="27" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="132"/>
+    <row r="27" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="42"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="99"/>
-      <c r="G27" s="99"/>
-      <c r="H27" s="99"/>
-      <c r="I27" s="99"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="100"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="85"/>
       <c r="L27" s="31"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="108"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="108"/>
-      <c r="S27" s="109"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="114"/>
+      <c r="P27" s="114"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="115"/>
       <c r="T27" s="21"/>
       <c r="U27" s="21"/>
       <c r="V27" s="33"/>
@@ -2621,8 +2621,8 @@
       <c r="AE27" s="22"/>
       <c r="AK27" s="29"/>
     </row>
-    <row r="28" spans="2:44" ht="31.2" x14ac:dyDescent="0.4">
-      <c r="B28" s="132"/>
+    <row r="28" spans="2:44" ht="31.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="42"/>
       <c r="D28" s="20"/>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
@@ -2653,235 +2653,235 @@
       <c r="AE28" s="22"/>
       <c r="AQ28" s="27"/>
     </row>
-    <row r="29" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="132"/>
+    <row r="29" spans="2:44" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="42"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="110" t="s">
+      <c r="E29" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="112"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="87"/>
+      <c r="K29" s="88"/>
       <c r="L29" s="31"/>
-      <c r="M29" s="119" t="s">
+      <c r="M29" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="N29" s="120"/>
-      <c r="O29" s="120"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="120"/>
-      <c r="S29" s="121"/>
+      <c r="N29" s="96"/>
+      <c r="O29" s="96"/>
+      <c r="P29" s="96"/>
+      <c r="Q29" s="96"/>
+      <c r="R29" s="96"/>
+      <c r="S29" s="97"/>
       <c r="T29" s="21"/>
       <c r="U29" s="21"/>
       <c r="V29" s="33"/>
       <c r="W29" s="33"/>
       <c r="X29" s="33"/>
       <c r="Y29" s="33"/>
-      <c r="Z29" s="86" t="s">
+      <c r="Z29" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AA29" s="87"/>
+      <c r="AA29" s="63"/>
       <c r="AB29" s="33"/>
-      <c r="AC29" s="86" t="s">
+      <c r="AC29" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AD29" s="87"/>
+      <c r="AD29" s="63"/>
       <c r="AE29" s="22"/>
     </row>
-    <row r="30" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="132"/>
+    <row r="30" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="42"/>
       <c r="D30" s="20"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="115"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="91"/>
       <c r="L30" s="31"/>
-      <c r="M30" s="122"/>
-      <c r="N30" s="123"/>
-      <c r="O30" s="123"/>
-      <c r="P30" s="123"/>
-      <c r="Q30" s="123"/>
-      <c r="R30" s="123"/>
-      <c r="S30" s="124"/>
+      <c r="M30" s="98"/>
+      <c r="N30" s="99"/>
+      <c r="O30" s="99"/>
+      <c r="P30" s="99"/>
+      <c r="Q30" s="99"/>
+      <c r="R30" s="99"/>
+      <c r="S30" s="100"/>
       <c r="T30" s="21"/>
       <c r="U30" s="21"/>
       <c r="V30" s="33"/>
       <c r="W30" s="33"/>
       <c r="X30" s="33"/>
       <c r="Y30" s="33"/>
-      <c r="Z30" s="88"/>
-      <c r="AA30" s="89"/>
+      <c r="Z30" s="64"/>
+      <c r="AA30" s="65"/>
       <c r="AB30" s="33"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="89"/>
+      <c r="AC30" s="64"/>
+      <c r="AD30" s="65"/>
       <c r="AE30" s="22"/>
     </row>
-    <row r="31" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="132"/>
+    <row r="31" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="42"/>
       <c r="C31" s="13"/>
       <c r="D31" s="21"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="114"/>
-      <c r="G31" s="114"/>
-      <c r="H31" s="114"/>
-      <c r="I31" s="114"/>
-      <c r="J31" s="114"/>
-      <c r="K31" s="115"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="90"/>
+      <c r="H31" s="90"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="91"/>
       <c r="L31" s="31"/>
-      <c r="M31" s="122"/>
-      <c r="N31" s="123"/>
-      <c r="O31" s="123"/>
-      <c r="P31" s="123"/>
-      <c r="Q31" s="123"/>
-      <c r="R31" s="123"/>
-      <c r="S31" s="124"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="99"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="99"/>
+      <c r="Q31" s="99"/>
+      <c r="R31" s="99"/>
+      <c r="S31" s="100"/>
       <c r="T31" s="21"/>
       <c r="U31" s="21"/>
       <c r="V31" s="33"/>
       <c r="W31" s="33"/>
       <c r="X31" s="33"/>
       <c r="Y31" s="33"/>
-      <c r="Z31" s="88"/>
-      <c r="AA31" s="89"/>
+      <c r="Z31" s="64"/>
+      <c r="AA31" s="65"/>
       <c r="AB31" s="33"/>
-      <c r="AC31" s="88"/>
-      <c r="AD31" s="89"/>
+      <c r="AC31" s="64"/>
+      <c r="AD31" s="65"/>
       <c r="AE31" s="22"/>
     </row>
-    <row r="32" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="132"/>
+    <row r="32" spans="2:44" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="42"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
-      <c r="G32" s="114"/>
-      <c r="H32" s="114"/>
-      <c r="I32" s="114"/>
-      <c r="J32" s="114"/>
-      <c r="K32" s="115"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="90"/>
+      <c r="G32" s="90"/>
+      <c r="H32" s="90"/>
+      <c r="I32" s="90"/>
+      <c r="J32" s="90"/>
+      <c r="K32" s="91"/>
       <c r="L32" s="31"/>
-      <c r="M32" s="122"/>
-      <c r="N32" s="123"/>
-      <c r="O32" s="123"/>
-      <c r="P32" s="123"/>
-      <c r="Q32" s="123"/>
-      <c r="R32" s="123"/>
-      <c r="S32" s="124"/>
+      <c r="M32" s="98"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="99"/>
+      <c r="S32" s="100"/>
       <c r="T32" s="21"/>
       <c r="U32" s="21"/>
       <c r="V32" s="33"/>
       <c r="W32" s="33"/>
       <c r="X32" s="33"/>
       <c r="Y32" s="33"/>
-      <c r="Z32" s="88"/>
-      <c r="AA32" s="89"/>
+      <c r="Z32" s="64"/>
+      <c r="AA32" s="65"/>
       <c r="AB32" s="33"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="89"/>
+      <c r="AC32" s="64"/>
+      <c r="AD32" s="65"/>
       <c r="AE32" s="22"/>
       <c r="AL32" s="30"/>
     </row>
-    <row r="33" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="132"/>
+    <row r="33" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="42"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="113"/>
-      <c r="F33" s="114"/>
-      <c r="G33" s="114"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="114"/>
-      <c r="J33" s="114"/>
-      <c r="K33" s="115"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="90"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="90"/>
+      <c r="I33" s="90"/>
+      <c r="J33" s="90"/>
+      <c r="K33" s="91"/>
       <c r="L33" s="31"/>
-      <c r="M33" s="122"/>
-      <c r="N33" s="123"/>
-      <c r="O33" s="123"/>
-      <c r="P33" s="123"/>
-      <c r="Q33" s="123"/>
-      <c r="R33" s="123"/>
-      <c r="S33" s="124"/>
+      <c r="M33" s="98"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="99"/>
+      <c r="R33" s="99"/>
+      <c r="S33" s="100"/>
       <c r="T33" s="21"/>
       <c r="U33" s="21"/>
       <c r="V33" s="33"/>
       <c r="W33" s="33"/>
       <c r="X33" s="33"/>
       <c r="Y33" s="33"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="89"/>
+      <c r="Z33" s="64"/>
+      <c r="AA33" s="65"/>
       <c r="AB33" s="33"/>
-      <c r="AC33" s="88"/>
-      <c r="AD33" s="89"/>
+      <c r="AC33" s="64"/>
+      <c r="AD33" s="65"/>
       <c r="AE33" s="22"/>
     </row>
-    <row r="34" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="132"/>
+    <row r="34" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="42"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="113"/>
-      <c r="F34" s="114"/>
-      <c r="G34" s="114"/>
-      <c r="H34" s="114"/>
-      <c r="I34" s="114"/>
-      <c r="J34" s="114"/>
-      <c r="K34" s="115"/>
+      <c r="E34" s="89"/>
+      <c r="F34" s="90"/>
+      <c r="G34" s="90"/>
+      <c r="H34" s="90"/>
+      <c r="I34" s="90"/>
+      <c r="J34" s="90"/>
+      <c r="K34" s="91"/>
       <c r="L34" s="31"/>
-      <c r="M34" s="122"/>
-      <c r="N34" s="123"/>
-      <c r="O34" s="123"/>
-      <c r="P34" s="123"/>
-      <c r="Q34" s="123"/>
-      <c r="R34" s="123"/>
-      <c r="S34" s="124"/>
+      <c r="M34" s="98"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="99"/>
+      <c r="S34" s="100"/>
       <c r="T34" s="21"/>
       <c r="U34" s="21"/>
       <c r="V34" s="33"/>
       <c r="W34" s="33"/>
       <c r="X34" s="33"/>
       <c r="Y34" s="33"/>
-      <c r="Z34" s="88"/>
-      <c r="AA34" s="89"/>
+      <c r="Z34" s="64"/>
+      <c r="AA34" s="65"/>
       <c r="AB34" s="33"/>
-      <c r="AC34" s="88"/>
-      <c r="AD34" s="89"/>
+      <c r="AC34" s="64"/>
+      <c r="AD34" s="65"/>
       <c r="AE34" s="22"/>
     </row>
-    <row r="35" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="132"/>
+    <row r="35" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="42"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117"/>
-      <c r="H35" s="117"/>
-      <c r="I35" s="117"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="118"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
+      <c r="J35" s="93"/>
+      <c r="K35" s="94"/>
       <c r="L35" s="31"/>
-      <c r="M35" s="125"/>
-      <c r="N35" s="126"/>
-      <c r="O35" s="126"/>
-      <c r="P35" s="126"/>
-      <c r="Q35" s="126"/>
-      <c r="R35" s="126"/>
-      <c r="S35" s="127"/>
+      <c r="M35" s="101"/>
+      <c r="N35" s="102"/>
+      <c r="O35" s="102"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="102"/>
+      <c r="S35" s="103"/>
       <c r="T35" s="21"/>
       <c r="U35" s="21"/>
       <c r="V35" s="33"/>
       <c r="W35" s="33"/>
       <c r="X35" s="33"/>
       <c r="Y35" s="33"/>
-      <c r="Z35" s="90"/>
-      <c r="AA35" s="91"/>
+      <c r="Z35" s="66"/>
+      <c r="AA35" s="67"/>
       <c r="AB35" s="33"/>
-      <c r="AC35" s="90"/>
-      <c r="AD35" s="91"/>
+      <c r="AC35" s="66"/>
+      <c r="AD35" s="67"/>
       <c r="AE35" s="22"/>
     </row>
-    <row r="36" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B36" s="132"/>
+    <row r="36" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B36" s="42"/>
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
@@ -2911,8 +2911,8 @@
       <c r="AD36" s="21"/>
       <c r="AE36" s="22"/>
     </row>
-    <row r="37" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B37" s="132"/>
+    <row r="37" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B37" s="42"/>
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
@@ -2942,19 +2942,19 @@
       <c r="AD37" s="21"/>
       <c r="AE37" s="22"/>
     </row>
-    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="132"/>
+    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="42"/>
       <c r="D38" s="20"/>
       <c r="E38" s="33"/>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="117" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="43"/>
-      <c r="H38" s="48" t="s">
+      <c r="G38" s="118"/>
+      <c r="H38" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="I38" s="49"/>
-      <c r="J38" s="50"/>
+      <c r="I38" s="124"/>
+      <c r="J38" s="125"/>
       <c r="K38" s="33"/>
       <c r="L38" s="33"/>
       <c r="M38" s="33"/>
@@ -2977,15 +2977,15 @@
       <c r="AD38" s="34"/>
       <c r="AE38" s="22"/>
     </row>
-    <row r="39" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B39" s="132"/>
+    <row r="39" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="42"/>
       <c r="D39" s="20"/>
       <c r="E39" s="33"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="53"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="120"/>
+      <c r="H39" s="126"/>
+      <c r="I39" s="127"/>
+      <c r="J39" s="128"/>
       <c r="K39" s="33"/>
       <c r="L39" s="33"/>
       <c r="M39" s="33"/>
@@ -2996,150 +2996,150 @@
       <c r="R39" s="33"/>
       <c r="S39" s="33"/>
       <c r="T39" s="33"/>
-      <c r="U39" s="57" t="s">
+      <c r="U39" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="V39" s="58"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="58"/>
-      <c r="Y39" s="58"/>
-      <c r="Z39" s="58"/>
-      <c r="AA39" s="59"/>
+      <c r="V39" s="133"/>
+      <c r="W39" s="133"/>
+      <c r="X39" s="133"/>
+      <c r="Y39" s="133"/>
+      <c r="Z39" s="133"/>
+      <c r="AA39" s="134"/>
       <c r="AB39" s="34"/>
       <c r="AC39" s="34"/>
       <c r="AD39" s="34"/>
       <c r="AE39" s="22"/>
     </row>
-    <row r="40" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B40" s="132"/>
+    <row r="40" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B40" s="42"/>
       <c r="D40" s="20"/>
       <c r="E40" s="33"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="53"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="122"/>
+      <c r="H40" s="126"/>
+      <c r="I40" s="127"/>
+      <c r="J40" s="128"/>
       <c r="K40" s="33"/>
       <c r="L40" s="33"/>
       <c r="M40" s="33"/>
-      <c r="N40" s="65" t="s">
+      <c r="N40" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="O40" s="66"/>
-      <c r="P40" s="66"/>
-      <c r="Q40" s="66"/>
-      <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
-      <c r="U40" s="60"/>
-      <c r="V40" s="61"/>
-      <c r="W40" s="61"/>
-      <c r="X40" s="61"/>
-      <c r="Y40" s="61"/>
-      <c r="Z40" s="61"/>
-      <c r="AA40" s="62"/>
+      <c r="O40" s="141"/>
+      <c r="P40" s="141"/>
+      <c r="Q40" s="141"/>
+      <c r="R40" s="141"/>
+      <c r="S40" s="141"/>
+      <c r="T40" s="141"/>
+      <c r="U40" s="135"/>
+      <c r="V40" s="136"/>
+      <c r="W40" s="136"/>
+      <c r="X40" s="136"/>
+      <c r="Y40" s="136"/>
+      <c r="Z40" s="136"/>
+      <c r="AA40" s="137"/>
       <c r="AB40" s="34"/>
       <c r="AC40" s="34"/>
       <c r="AD40" s="34"/>
       <c r="AE40" s="22"/>
     </row>
-    <row r="41" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="132"/>
+    <row r="41" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="42"/>
       <c r="D41" s="20"/>
       <c r="E41" s="33"/>
       <c r="F41" s="34"/>
       <c r="G41" s="34"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="53"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="127"/>
+      <c r="J41" s="128"/>
       <c r="K41" s="33"/>
       <c r="L41" s="33"/>
       <c r="M41" s="33"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="68"/>
-      <c r="R41" s="68"/>
-      <c r="S41" s="68"/>
-      <c r="T41" s="68"/>
-      <c r="U41" s="60"/>
-      <c r="V41" s="61"/>
-      <c r="W41" s="61"/>
-      <c r="X41" s="61"/>
-      <c r="Y41" s="61"/>
-      <c r="Z41" s="61"/>
-      <c r="AA41" s="61"/>
-      <c r="AB41" s="71" t="s">
+      <c r="N41" s="142"/>
+      <c r="O41" s="143"/>
+      <c r="P41" s="143"/>
+      <c r="Q41" s="143"/>
+      <c r="R41" s="143"/>
+      <c r="S41" s="143"/>
+      <c r="T41" s="143"/>
+      <c r="U41" s="135"/>
+      <c r="V41" s="136"/>
+      <c r="W41" s="136"/>
+      <c r="X41" s="136"/>
+      <c r="Y41" s="136"/>
+      <c r="Z41" s="136"/>
+      <c r="AA41" s="136"/>
+      <c r="AB41" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="AC41" s="72"/>
-      <c r="AD41" s="73"/>
+      <c r="AC41" s="147"/>
+      <c r="AD41" s="148"/>
       <c r="AE41" s="22"/>
     </row>
-    <row r="42" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B42" s="132"/>
+    <row r="42" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B42" s="42"/>
       <c r="D42" s="20"/>
       <c r="E42" s="33"/>
       <c r="F42" s="33"/>
       <c r="G42" s="35"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="53"/>
+      <c r="H42" s="126"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="128"/>
       <c r="K42" s="33"/>
       <c r="L42" s="33"/>
       <c r="M42" s="33"/>
-      <c r="N42" s="67"/>
-      <c r="O42" s="68"/>
-      <c r="P42" s="68"/>
-      <c r="Q42" s="68"/>
-      <c r="R42" s="68"/>
-      <c r="S42" s="68"/>
-      <c r="T42" s="68"/>
-      <c r="U42" s="60"/>
-      <c r="V42" s="61"/>
-      <c r="W42" s="61"/>
-      <c r="X42" s="61"/>
-      <c r="Y42" s="61"/>
-      <c r="Z42" s="61"/>
-      <c r="AA42" s="61"/>
-      <c r="AB42" s="74"/>
-      <c r="AC42" s="75"/>
-      <c r="AD42" s="76"/>
+      <c r="N42" s="142"/>
+      <c r="O42" s="143"/>
+      <c r="P42" s="143"/>
+      <c r="Q42" s="143"/>
+      <c r="R42" s="143"/>
+      <c r="S42" s="143"/>
+      <c r="T42" s="143"/>
+      <c r="U42" s="135"/>
+      <c r="V42" s="136"/>
+      <c r="W42" s="136"/>
+      <c r="X42" s="136"/>
+      <c r="Y42" s="136"/>
+      <c r="Z42" s="136"/>
+      <c r="AA42" s="136"/>
+      <c r="AB42" s="149"/>
+      <c r="AC42" s="150"/>
+      <c r="AD42" s="151"/>
       <c r="AE42" s="22"/>
     </row>
-    <row r="43" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B43" s="132"/>
+    <row r="43" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B43" s="42"/>
       <c r="D43" s="20"/>
       <c r="E43" s="33"/>
       <c r="F43" s="33"/>
       <c r="G43" s="33"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="56"/>
+      <c r="H43" s="129"/>
+      <c r="I43" s="130"/>
+      <c r="J43" s="131"/>
       <c r="K43" s="33"/>
       <c r="L43" s="33"/>
       <c r="M43" s="33"/>
-      <c r="N43" s="67"/>
-      <c r="O43" s="68"/>
-      <c r="P43" s="68"/>
-      <c r="Q43" s="68"/>
-      <c r="R43" s="68"/>
-      <c r="S43" s="68"/>
-      <c r="T43" s="68"/>
-      <c r="U43" s="60"/>
-      <c r="V43" s="61"/>
-      <c r="W43" s="61"/>
-      <c r="X43" s="61"/>
-      <c r="Y43" s="61"/>
-      <c r="Z43" s="61"/>
-      <c r="AA43" s="61"/>
-      <c r="AB43" s="74"/>
-      <c r="AC43" s="75"/>
-      <c r="AD43" s="76"/>
+      <c r="N43" s="142"/>
+      <c r="O43" s="143"/>
+      <c r="P43" s="143"/>
+      <c r="Q43" s="143"/>
+      <c r="R43" s="143"/>
+      <c r="S43" s="143"/>
+      <c r="T43" s="143"/>
+      <c r="U43" s="135"/>
+      <c r="V43" s="136"/>
+      <c r="W43" s="136"/>
+      <c r="X43" s="136"/>
+      <c r="Y43" s="136"/>
+      <c r="Z43" s="136"/>
+      <c r="AA43" s="136"/>
+      <c r="AB43" s="149"/>
+      <c r="AC43" s="150"/>
+      <c r="AD43" s="151"/>
       <c r="AE43" s="22"/>
     </row>
-    <row r="44" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B44" s="132"/>
+    <row r="44" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B44" s="42"/>
       <c r="D44" s="20"/>
       <c r="E44" s="33"/>
       <c r="F44" s="33"/>
@@ -3150,27 +3150,27 @@
       <c r="K44" s="33"/>
       <c r="L44" s="33"/>
       <c r="M44" s="33"/>
-      <c r="N44" s="67"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="68"/>
-      <c r="Q44" s="68"/>
-      <c r="R44" s="68"/>
-      <c r="S44" s="68"/>
-      <c r="T44" s="68"/>
-      <c r="U44" s="60"/>
-      <c r="V44" s="61"/>
-      <c r="W44" s="61"/>
-      <c r="X44" s="61"/>
-      <c r="Y44" s="61"/>
-      <c r="Z44" s="61"/>
-      <c r="AA44" s="61"/>
-      <c r="AB44" s="74"/>
-      <c r="AC44" s="75"/>
-      <c r="AD44" s="76"/>
+      <c r="N44" s="142"/>
+      <c r="O44" s="143"/>
+      <c r="P44" s="143"/>
+      <c r="Q44" s="143"/>
+      <c r="R44" s="143"/>
+      <c r="S44" s="143"/>
+      <c r="T44" s="143"/>
+      <c r="U44" s="135"/>
+      <c r="V44" s="136"/>
+      <c r="W44" s="136"/>
+      <c r="X44" s="136"/>
+      <c r="Y44" s="136"/>
+      <c r="Z44" s="136"/>
+      <c r="AA44" s="136"/>
+      <c r="AB44" s="149"/>
+      <c r="AC44" s="150"/>
+      <c r="AD44" s="151"/>
       <c r="AE44" s="22"/>
     </row>
-    <row r="45" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B45" s="132"/>
+    <row r="45" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B45" s="42"/>
       <c r="D45" s="20"/>
       <c r="E45" s="33"/>
       <c r="F45" s="33"/>
@@ -3181,35 +3181,35 @@
       <c r="K45" s="33"/>
       <c r="L45" s="33"/>
       <c r="M45" s="33"/>
-      <c r="N45" s="69"/>
-      <c r="O45" s="70"/>
-      <c r="P45" s="70"/>
-      <c r="Q45" s="70"/>
-      <c r="R45" s="70"/>
-      <c r="S45" s="70"/>
-      <c r="T45" s="70"/>
-      <c r="U45" s="63"/>
-      <c r="V45" s="64"/>
-      <c r="W45" s="64"/>
-      <c r="X45" s="64"/>
-      <c r="Y45" s="64"/>
-      <c r="Z45" s="64"/>
-      <c r="AA45" s="64"/>
-      <c r="AB45" s="77"/>
-      <c r="AC45" s="78"/>
-      <c r="AD45" s="79"/>
+      <c r="N45" s="144"/>
+      <c r="O45" s="145"/>
+      <c r="P45" s="145"/>
+      <c r="Q45" s="145"/>
+      <c r="R45" s="145"/>
+      <c r="S45" s="145"/>
+      <c r="T45" s="145"/>
+      <c r="U45" s="138"/>
+      <c r="V45" s="139"/>
+      <c r="W45" s="139"/>
+      <c r="X45" s="139"/>
+      <c r="Y45" s="139"/>
+      <c r="Z45" s="139"/>
+      <c r="AA45" s="139"/>
+      <c r="AB45" s="152"/>
+      <c r="AC45" s="153"/>
+      <c r="AD45" s="154"/>
       <c r="AE45" s="22"/>
     </row>
-    <row r="46" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B46" s="132"/>
+    <row r="46" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B46" s="42"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="80" t="s">
+      <c r="E46" s="155" t="s">
         <v>0</v>
       </c>
-      <c r="F46" s="81"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="81"/>
-      <c r="I46" s="82"/>
+      <c r="F46" s="156"/>
+      <c r="G46" s="156"/>
+      <c r="H46" s="156"/>
+      <c r="I46" s="157"/>
       <c r="J46" s="33"/>
       <c r="K46" s="33"/>
       <c r="L46" s="33"/>
@@ -3233,14 +3233,14 @@
       <c r="AD46" s="33"/>
       <c r="AE46" s="22"/>
     </row>
-    <row r="47" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B47" s="133"/>
+    <row r="47" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="43"/>
       <c r="D47" s="23"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="84"/>
-      <c r="G47" s="84"/>
-      <c r="H47" s="84"/>
-      <c r="I47" s="85"/>
+      <c r="E47" s="158"/>
+      <c r="F47" s="159"/>
+      <c r="G47" s="159"/>
+      <c r="H47" s="159"/>
+      <c r="I47" s="160"/>
       <c r="J47" s="36"/>
       <c r="K47" s="36"/>
       <c r="L47" s="36"/>
@@ -3264,317 +3264,317 @@
       <c r="AD47" s="36"/>
       <c r="AE47" s="24"/>
     </row>
-    <row r="59" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA59" s="41" t="s">
+    <row r="59" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA59" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB59" s="41"/>
-      <c r="BC59" s="41"/>
-      <c r="BD59" s="41"/>
-      <c r="BE59" s="41"/>
-      <c r="BF59" s="41"/>
-      <c r="BG59" s="41"/>
-      <c r="BI59" s="41" t="s">
+      <c r="BB59" s="116"/>
+      <c r="BC59" s="116"/>
+      <c r="BD59" s="116"/>
+      <c r="BE59" s="116"/>
+      <c r="BF59" s="116"/>
+      <c r="BG59" s="116"/>
+      <c r="BI59" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BJ59" s="41"/>
-      <c r="BK59" s="41"/>
-      <c r="BL59" s="41"/>
-      <c r="BM59" s="41"/>
-      <c r="BN59" s="41"/>
-      <c r="BO59" s="41"/>
-    </row>
-    <row r="60" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA60" s="41"/>
-      <c r="BB60" s="41"/>
-      <c r="BC60" s="41"/>
-      <c r="BD60" s="41"/>
-      <c r="BE60" s="41"/>
-      <c r="BF60" s="41"/>
-      <c r="BG60" s="41"/>
-      <c r="BI60" s="41"/>
-      <c r="BJ60" s="41"/>
-      <c r="BK60" s="41"/>
-      <c r="BL60" s="41"/>
-      <c r="BM60" s="41"/>
-      <c r="BN60" s="41"/>
-      <c r="BO60" s="41"/>
-    </row>
-    <row r="61" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA61" s="41"/>
-      <c r="BB61" s="41"/>
-      <c r="BC61" s="41"/>
-      <c r="BD61" s="41"/>
-      <c r="BE61" s="41"/>
-      <c r="BF61" s="41"/>
-      <c r="BG61" s="41"/>
-      <c r="BI61" s="41"/>
-      <c r="BJ61" s="41"/>
-      <c r="BK61" s="41"/>
-      <c r="BL61" s="41"/>
-      <c r="BM61" s="41"/>
-      <c r="BN61" s="41"/>
-      <c r="BO61" s="41"/>
-    </row>
-    <row r="62" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA62" s="41"/>
-      <c r="BB62" s="41"/>
-      <c r="BC62" s="41"/>
-      <c r="BD62" s="41"/>
-      <c r="BE62" s="41"/>
-      <c r="BF62" s="41"/>
-      <c r="BG62" s="41"/>
-      <c r="BI62" s="41"/>
-      <c r="BJ62" s="41"/>
-      <c r="BK62" s="41"/>
-      <c r="BL62" s="41"/>
-      <c r="BM62" s="41"/>
-      <c r="BN62" s="41"/>
-      <c r="BO62" s="41"/>
-    </row>
-    <row r="63" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA63" s="41"/>
-      <c r="BB63" s="41"/>
-      <c r="BC63" s="41"/>
-      <c r="BD63" s="41"/>
-      <c r="BE63" s="41"/>
-      <c r="BF63" s="41"/>
-      <c r="BG63" s="41"/>
-      <c r="BI63" s="41"/>
-      <c r="BJ63" s="41"/>
-      <c r="BK63" s="41"/>
-      <c r="BL63" s="41"/>
-      <c r="BM63" s="41"/>
-      <c r="BN63" s="41"/>
-      <c r="BO63" s="41"/>
-    </row>
-    <row r="64" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA64" s="41"/>
-      <c r="BB64" s="41"/>
-      <c r="BC64" s="41"/>
-      <c r="BD64" s="41"/>
-      <c r="BE64" s="41"/>
-      <c r="BF64" s="41"/>
-      <c r="BG64" s="41"/>
-      <c r="BI64" s="41"/>
-      <c r="BJ64" s="41"/>
-      <c r="BK64" s="41"/>
-      <c r="BL64" s="41"/>
-      <c r="BM64" s="41"/>
-      <c r="BN64" s="41"/>
-      <c r="BO64" s="41"/>
-    </row>
-    <row r="66" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA66" s="41" t="s">
+      <c r="BJ59" s="116"/>
+      <c r="BK59" s="116"/>
+      <c r="BL59" s="116"/>
+      <c r="BM59" s="116"/>
+      <c r="BN59" s="116"/>
+      <c r="BO59" s="116"/>
+    </row>
+    <row r="60" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA60" s="116"/>
+      <c r="BB60" s="116"/>
+      <c r="BC60" s="116"/>
+      <c r="BD60" s="116"/>
+      <c r="BE60" s="116"/>
+      <c r="BF60" s="116"/>
+      <c r="BG60" s="116"/>
+      <c r="BI60" s="116"/>
+      <c r="BJ60" s="116"/>
+      <c r="BK60" s="116"/>
+      <c r="BL60" s="116"/>
+      <c r="BM60" s="116"/>
+      <c r="BN60" s="116"/>
+      <c r="BO60" s="116"/>
+    </row>
+    <row r="61" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA61" s="116"/>
+      <c r="BB61" s="116"/>
+      <c r="BC61" s="116"/>
+      <c r="BD61" s="116"/>
+      <c r="BE61" s="116"/>
+      <c r="BF61" s="116"/>
+      <c r="BG61" s="116"/>
+      <c r="BI61" s="116"/>
+      <c r="BJ61" s="116"/>
+      <c r="BK61" s="116"/>
+      <c r="BL61" s="116"/>
+      <c r="BM61" s="116"/>
+      <c r="BN61" s="116"/>
+      <c r="BO61" s="116"/>
+    </row>
+    <row r="62" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA62" s="116"/>
+      <c r="BB62" s="116"/>
+      <c r="BC62" s="116"/>
+      <c r="BD62" s="116"/>
+      <c r="BE62" s="116"/>
+      <c r="BF62" s="116"/>
+      <c r="BG62" s="116"/>
+      <c r="BI62" s="116"/>
+      <c r="BJ62" s="116"/>
+      <c r="BK62" s="116"/>
+      <c r="BL62" s="116"/>
+      <c r="BM62" s="116"/>
+      <c r="BN62" s="116"/>
+      <c r="BO62" s="116"/>
+    </row>
+    <row r="63" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA63" s="116"/>
+      <c r="BB63" s="116"/>
+      <c r="BC63" s="116"/>
+      <c r="BD63" s="116"/>
+      <c r="BE63" s="116"/>
+      <c r="BF63" s="116"/>
+      <c r="BG63" s="116"/>
+      <c r="BI63" s="116"/>
+      <c r="BJ63" s="116"/>
+      <c r="BK63" s="116"/>
+      <c r="BL63" s="116"/>
+      <c r="BM63" s="116"/>
+      <c r="BN63" s="116"/>
+      <c r="BO63" s="116"/>
+    </row>
+    <row r="64" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA64" s="116"/>
+      <c r="BB64" s="116"/>
+      <c r="BC64" s="116"/>
+      <c r="BD64" s="116"/>
+      <c r="BE64" s="116"/>
+      <c r="BF64" s="116"/>
+      <c r="BG64" s="116"/>
+      <c r="BI64" s="116"/>
+      <c r="BJ64" s="116"/>
+      <c r="BK64" s="116"/>
+      <c r="BL64" s="116"/>
+      <c r="BM64" s="116"/>
+      <c r="BN64" s="116"/>
+      <c r="BO64" s="116"/>
+    </row>
+    <row r="66" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA66" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB66" s="41"/>
-      <c r="BC66" s="41"/>
-      <c r="BD66" s="41"/>
-      <c r="BE66" s="41"/>
-      <c r="BF66" s="41"/>
-      <c r="BG66" s="41"/>
-      <c r="BI66" s="41" t="s">
+      <c r="BB66" s="116"/>
+      <c r="BC66" s="116"/>
+      <c r="BD66" s="116"/>
+      <c r="BE66" s="116"/>
+      <c r="BF66" s="116"/>
+      <c r="BG66" s="116"/>
+      <c r="BI66" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BJ66" s="41"/>
-      <c r="BK66" s="41"/>
-      <c r="BL66" s="41"/>
-      <c r="BM66" s="41"/>
-      <c r="BN66" s="41"/>
-      <c r="BO66" s="41"/>
-    </row>
-    <row r="67" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA67" s="41"/>
-      <c r="BB67" s="41"/>
-      <c r="BC67" s="41"/>
-      <c r="BD67" s="41"/>
-      <c r="BE67" s="41"/>
-      <c r="BF67" s="41"/>
-      <c r="BG67" s="41"/>
-      <c r="BI67" s="41"/>
-      <c r="BJ67" s="41"/>
-      <c r="BK67" s="41"/>
-      <c r="BL67" s="41"/>
-      <c r="BM67" s="41"/>
-      <c r="BN67" s="41"/>
-      <c r="BO67" s="41"/>
-    </row>
-    <row r="68" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA68" s="41"/>
-      <c r="BB68" s="41"/>
-      <c r="BC68" s="41"/>
-      <c r="BD68" s="41"/>
-      <c r="BE68" s="41"/>
-      <c r="BF68" s="41"/>
-      <c r="BG68" s="41"/>
-      <c r="BI68" s="41"/>
-      <c r="BJ68" s="41"/>
-      <c r="BK68" s="41"/>
-      <c r="BL68" s="41"/>
-      <c r="BM68" s="41"/>
-      <c r="BN68" s="41"/>
-      <c r="BO68" s="41"/>
-    </row>
-    <row r="69" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA69" s="41"/>
-      <c r="BB69" s="41"/>
-      <c r="BC69" s="41"/>
-      <c r="BD69" s="41"/>
-      <c r="BE69" s="41"/>
-      <c r="BF69" s="41"/>
-      <c r="BG69" s="41"/>
-      <c r="BI69" s="41"/>
-      <c r="BJ69" s="41"/>
-      <c r="BK69" s="41"/>
-      <c r="BL69" s="41"/>
-      <c r="BM69" s="41"/>
-      <c r="BN69" s="41"/>
-      <c r="BO69" s="41"/>
-    </row>
-    <row r="70" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA70" s="41"/>
-      <c r="BB70" s="41"/>
-      <c r="BC70" s="41"/>
-      <c r="BD70" s="41"/>
-      <c r="BE70" s="41"/>
-      <c r="BF70" s="41"/>
-      <c r="BG70" s="41"/>
-      <c r="BI70" s="41"/>
-      <c r="BJ70" s="41"/>
-      <c r="BK70" s="41"/>
-      <c r="BL70" s="41"/>
-      <c r="BM70" s="41"/>
-      <c r="BN70" s="41"/>
-      <c r="BO70" s="41"/>
-    </row>
-    <row r="71" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA71" s="41"/>
-      <c r="BB71" s="41"/>
-      <c r="BC71" s="41"/>
-      <c r="BD71" s="41"/>
-      <c r="BE71" s="41"/>
-      <c r="BF71" s="41"/>
-      <c r="BG71" s="41"/>
-      <c r="BI71" s="41"/>
-      <c r="BJ71" s="41"/>
-      <c r="BK71" s="41"/>
-      <c r="BL71" s="41"/>
-      <c r="BM71" s="41"/>
-      <c r="BN71" s="41"/>
-      <c r="BO71" s="41"/>
-    </row>
-    <row r="73" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA73" s="41" t="s">
+      <c r="BJ66" s="116"/>
+      <c r="BK66" s="116"/>
+      <c r="BL66" s="116"/>
+      <c r="BM66" s="116"/>
+      <c r="BN66" s="116"/>
+      <c r="BO66" s="116"/>
+    </row>
+    <row r="67" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA67" s="116"/>
+      <c r="BB67" s="116"/>
+      <c r="BC67" s="116"/>
+      <c r="BD67" s="116"/>
+      <c r="BE67" s="116"/>
+      <c r="BF67" s="116"/>
+      <c r="BG67" s="116"/>
+      <c r="BI67" s="116"/>
+      <c r="BJ67" s="116"/>
+      <c r="BK67" s="116"/>
+      <c r="BL67" s="116"/>
+      <c r="BM67" s="116"/>
+      <c r="BN67" s="116"/>
+      <c r="BO67" s="116"/>
+    </row>
+    <row r="68" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA68" s="116"/>
+      <c r="BB68" s="116"/>
+      <c r="BC68" s="116"/>
+      <c r="BD68" s="116"/>
+      <c r="BE68" s="116"/>
+      <c r="BF68" s="116"/>
+      <c r="BG68" s="116"/>
+      <c r="BI68" s="116"/>
+      <c r="BJ68" s="116"/>
+      <c r="BK68" s="116"/>
+      <c r="BL68" s="116"/>
+      <c r="BM68" s="116"/>
+      <c r="BN68" s="116"/>
+      <c r="BO68" s="116"/>
+    </row>
+    <row r="69" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA69" s="116"/>
+      <c r="BB69" s="116"/>
+      <c r="BC69" s="116"/>
+      <c r="BD69" s="116"/>
+      <c r="BE69" s="116"/>
+      <c r="BF69" s="116"/>
+      <c r="BG69" s="116"/>
+      <c r="BI69" s="116"/>
+      <c r="BJ69" s="116"/>
+      <c r="BK69" s="116"/>
+      <c r="BL69" s="116"/>
+      <c r="BM69" s="116"/>
+      <c r="BN69" s="116"/>
+      <c r="BO69" s="116"/>
+    </row>
+    <row r="70" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA70" s="116"/>
+      <c r="BB70" s="116"/>
+      <c r="BC70" s="116"/>
+      <c r="BD70" s="116"/>
+      <c r="BE70" s="116"/>
+      <c r="BF70" s="116"/>
+      <c r="BG70" s="116"/>
+      <c r="BI70" s="116"/>
+      <c r="BJ70" s="116"/>
+      <c r="BK70" s="116"/>
+      <c r="BL70" s="116"/>
+      <c r="BM70" s="116"/>
+      <c r="BN70" s="116"/>
+      <c r="BO70" s="116"/>
+    </row>
+    <row r="71" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA71" s="116"/>
+      <c r="BB71" s="116"/>
+      <c r="BC71" s="116"/>
+      <c r="BD71" s="116"/>
+      <c r="BE71" s="116"/>
+      <c r="BF71" s="116"/>
+      <c r="BG71" s="116"/>
+      <c r="BI71" s="116"/>
+      <c r="BJ71" s="116"/>
+      <c r="BK71" s="116"/>
+      <c r="BL71" s="116"/>
+      <c r="BM71" s="116"/>
+      <c r="BN71" s="116"/>
+      <c r="BO71" s="116"/>
+    </row>
+    <row r="73" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA73" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB73" s="41"/>
-      <c r="BC73" s="41"/>
-      <c r="BD73" s="41"/>
-      <c r="BE73" s="41"/>
-      <c r="BF73" s="41"/>
-      <c r="BG73" s="41"/>
-    </row>
-    <row r="74" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA74" s="41"/>
-      <c r="BB74" s="41"/>
-      <c r="BC74" s="41"/>
-      <c r="BD74" s="41"/>
-      <c r="BE74" s="41"/>
-      <c r="BF74" s="41"/>
-      <c r="BG74" s="41"/>
-    </row>
-    <row r="75" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA75" s="41"/>
-      <c r="BB75" s="41"/>
-      <c r="BC75" s="41"/>
-      <c r="BD75" s="41"/>
-      <c r="BE75" s="41"/>
-      <c r="BF75" s="41"/>
-      <c r="BG75" s="41"/>
-    </row>
-    <row r="76" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA76" s="41"/>
-      <c r="BB76" s="41"/>
-      <c r="BC76" s="41"/>
-      <c r="BD76" s="41"/>
-      <c r="BE76" s="41"/>
-      <c r="BF76" s="41"/>
-      <c r="BG76" s="41"/>
-    </row>
-    <row r="77" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA77" s="41"/>
-      <c r="BB77" s="41"/>
-      <c r="BC77" s="41"/>
-      <c r="BD77" s="41"/>
-      <c r="BE77" s="41"/>
-      <c r="BF77" s="41"/>
-      <c r="BG77" s="41"/>
-    </row>
-    <row r="78" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA78" s="41"/>
-      <c r="BB78" s="41"/>
-      <c r="BC78" s="41"/>
-      <c r="BD78" s="41"/>
-      <c r="BE78" s="41"/>
-      <c r="BF78" s="41"/>
-      <c r="BG78" s="41"/>
-    </row>
-    <row r="80" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA80" s="41" t="s">
+      <c r="BB73" s="116"/>
+      <c r="BC73" s="116"/>
+      <c r="BD73" s="116"/>
+      <c r="BE73" s="116"/>
+      <c r="BF73" s="116"/>
+      <c r="BG73" s="116"/>
+    </row>
+    <row r="74" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA74" s="116"/>
+      <c r="BB74" s="116"/>
+      <c r="BC74" s="116"/>
+      <c r="BD74" s="116"/>
+      <c r="BE74" s="116"/>
+      <c r="BF74" s="116"/>
+      <c r="BG74" s="116"/>
+    </row>
+    <row r="75" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA75" s="116"/>
+      <c r="BB75" s="116"/>
+      <c r="BC75" s="116"/>
+      <c r="BD75" s="116"/>
+      <c r="BE75" s="116"/>
+      <c r="BF75" s="116"/>
+      <c r="BG75" s="116"/>
+    </row>
+    <row r="76" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA76" s="116"/>
+      <c r="BB76" s="116"/>
+      <c r="BC76" s="116"/>
+      <c r="BD76" s="116"/>
+      <c r="BE76" s="116"/>
+      <c r="BF76" s="116"/>
+      <c r="BG76" s="116"/>
+    </row>
+    <row r="77" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA77" s="116"/>
+      <c r="BB77" s="116"/>
+      <c r="BC77" s="116"/>
+      <c r="BD77" s="116"/>
+      <c r="BE77" s="116"/>
+      <c r="BF77" s="116"/>
+      <c r="BG77" s="116"/>
+    </row>
+    <row r="78" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA78" s="116"/>
+      <c r="BB78" s="116"/>
+      <c r="BC78" s="116"/>
+      <c r="BD78" s="116"/>
+      <c r="BE78" s="116"/>
+      <c r="BF78" s="116"/>
+      <c r="BG78" s="116"/>
+    </row>
+    <row r="80" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA80" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB80" s="41"/>
-      <c r="BC80" s="41"/>
-      <c r="BD80" s="41"/>
-      <c r="BE80" s="41"/>
-      <c r="BF80" s="41"/>
-      <c r="BG80" s="41"/>
-    </row>
-    <row r="81" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA81" s="41"/>
-      <c r="BB81" s="41"/>
-      <c r="BC81" s="41"/>
-      <c r="BD81" s="41"/>
-      <c r="BE81" s="41"/>
-      <c r="BF81" s="41"/>
-      <c r="BG81" s="41"/>
-    </row>
-    <row r="82" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA82" s="41"/>
-      <c r="BB82" s="41"/>
-      <c r="BC82" s="41"/>
-      <c r="BD82" s="41"/>
-      <c r="BE82" s="41"/>
-      <c r="BF82" s="41"/>
-      <c r="BG82" s="41"/>
-    </row>
-    <row r="83" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA83" s="41"/>
-      <c r="BB83" s="41"/>
-      <c r="BC83" s="41"/>
-      <c r="BD83" s="41"/>
-      <c r="BE83" s="41"/>
-      <c r="BF83" s="41"/>
-      <c r="BG83" s="41"/>
-    </row>
-    <row r="84" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA84" s="41"/>
-      <c r="BB84" s="41"/>
-      <c r="BC84" s="41"/>
-      <c r="BD84" s="41"/>
-      <c r="BE84" s="41"/>
-      <c r="BF84" s="41"/>
-      <c r="BG84" s="41"/>
-    </row>
-    <row r="85" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA85" s="41"/>
-      <c r="BB85" s="41"/>
-      <c r="BC85" s="41"/>
-      <c r="BD85" s="41"/>
-      <c r="BE85" s="41"/>
-      <c r="BF85" s="41"/>
-      <c r="BG85" s="41"/>
+      <c r="BB80" s="116"/>
+      <c r="BC80" s="116"/>
+      <c r="BD80" s="116"/>
+      <c r="BE80" s="116"/>
+      <c r="BF80" s="116"/>
+      <c r="BG80" s="116"/>
+    </row>
+    <row r="81" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA81" s="116"/>
+      <c r="BB81" s="116"/>
+      <c r="BC81" s="116"/>
+      <c r="BD81" s="116"/>
+      <c r="BE81" s="116"/>
+      <c r="BF81" s="116"/>
+      <c r="BG81" s="116"/>
+    </row>
+    <row r="82" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA82" s="116"/>
+      <c r="BB82" s="116"/>
+      <c r="BC82" s="116"/>
+      <c r="BD82" s="116"/>
+      <c r="BE82" s="116"/>
+      <c r="BF82" s="116"/>
+      <c r="BG82" s="116"/>
+    </row>
+    <row r="83" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA83" s="116"/>
+      <c r="BB83" s="116"/>
+      <c r="BC83" s="116"/>
+      <c r="BD83" s="116"/>
+      <c r="BE83" s="116"/>
+      <c r="BF83" s="116"/>
+      <c r="BG83" s="116"/>
+    </row>
+    <row r="84" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA84" s="116"/>
+      <c r="BB84" s="116"/>
+      <c r="BC84" s="116"/>
+      <c r="BD84" s="116"/>
+      <c r="BE84" s="116"/>
+      <c r="BF84" s="116"/>
+      <c r="BG84" s="116"/>
+    </row>
+    <row r="85" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA85" s="116"/>
+      <c r="BB85" s="116"/>
+      <c r="BC85" s="116"/>
+      <c r="BD85" s="116"/>
+      <c r="BE85" s="116"/>
+      <c r="BF85" s="116"/>
+      <c r="BG85" s="116"/>
       <c r="BH85" s="15"/>
       <c r="BI85" s="15"/>
       <c r="BJ85" s="15"/>
@@ -3587,6 +3587,24 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="BI59:BO64"/>
+    <mergeCell ref="BA66:BG71"/>
+    <mergeCell ref="BI66:BO71"/>
+    <mergeCell ref="BA73:BG78"/>
+    <mergeCell ref="BA80:BG85"/>
+    <mergeCell ref="F38:G40"/>
+    <mergeCell ref="H38:J43"/>
+    <mergeCell ref="U39:AA45"/>
+    <mergeCell ref="N40:T45"/>
+    <mergeCell ref="AB41:AD45"/>
+    <mergeCell ref="E46:I47"/>
+    <mergeCell ref="BA59:BG64"/>
+    <mergeCell ref="D2:AE2"/>
+    <mergeCell ref="W20:X26"/>
+    <mergeCell ref="Z20:AA26"/>
+    <mergeCell ref="AC20:AD26"/>
+    <mergeCell ref="E21:K27"/>
+    <mergeCell ref="M21:S27"/>
     <mergeCell ref="B4:B47"/>
     <mergeCell ref="E5:K11"/>
     <mergeCell ref="M5:S11"/>
@@ -3600,24 +3618,6 @@
     <mergeCell ref="M29:S35"/>
     <mergeCell ref="Z29:AA35"/>
     <mergeCell ref="AC29:AD35"/>
-    <mergeCell ref="D2:AE2"/>
-    <mergeCell ref="W20:X26"/>
-    <mergeCell ref="Z20:AA26"/>
-    <mergeCell ref="AC20:AD26"/>
-    <mergeCell ref="E21:K27"/>
-    <mergeCell ref="M21:S27"/>
-    <mergeCell ref="BA80:BG85"/>
-    <mergeCell ref="F38:G40"/>
-    <mergeCell ref="H38:J43"/>
-    <mergeCell ref="U39:AA45"/>
-    <mergeCell ref="N40:T45"/>
-    <mergeCell ref="AB41:AD45"/>
-    <mergeCell ref="E46:I47"/>
-    <mergeCell ref="BA59:BG64"/>
-    <mergeCell ref="BI59:BO64"/>
-    <mergeCell ref="BA66:BG71"/>
-    <mergeCell ref="BI66:BO71"/>
-    <mergeCell ref="BA73:BG78"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3626,9 +3626,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CCD9DD-BF32-4B35-BFB6-BD9E7663A4A2}">
   <dimension ref="B2:J37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C2" s="167" t="s">
         <v>1</v>
       </c>
@@ -3640,7 +3640,7 @@
       <c r="I2" s="168"/>
       <c r="J2" s="168"/>
     </row>
-    <row r="3" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B3" s="169" t="s">
         <v>2</v>
       </c>
@@ -3653,12 +3653,12 @@
       <c r="I3" s="2"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="169"/>
       <c r="C4" s="4"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="169"/>
       <c r="C5" s="4"/>
       <c r="D5" s="161" t="s">
@@ -3671,7 +3671,7 @@
       <c r="H5" s="162"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="169"/>
       <c r="C6" s="4"/>
       <c r="D6" s="163"/>
@@ -3680,7 +3680,7 @@
       <c r="H6" s="164"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="169"/>
       <c r="C7" s="4"/>
       <c r="D7" s="163"/>
@@ -3689,7 +3689,7 @@
       <c r="H7" s="164"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="169"/>
       <c r="C8" s="4"/>
       <c r="D8" s="165"/>
@@ -3698,12 +3698,12 @@
       <c r="H8" s="166"/>
       <c r="J8" s="5"/>
     </row>
-    <row r="9" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="169"/>
       <c r="C9" s="4"/>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="169"/>
       <c r="C10" s="4"/>
       <c r="D10" s="161" t="s">
@@ -3712,7 +3712,7 @@
       <c r="E10" s="162"/>
       <c r="J10" s="5"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="169"/>
       <c r="C11" s="4"/>
       <c r="D11" s="163"/>
@@ -3724,7 +3724,7 @@
       <c r="I11" s="162"/>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="169"/>
       <c r="C12" s="4"/>
       <c r="D12" s="163"/>
@@ -3734,14 +3734,14 @@
       <c r="I12" s="166"/>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="169"/>
       <c r="C13" s="4"/>
       <c r="D13" s="165"/>
       <c r="E13" s="166"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="169"/>
       <c r="C14" s="4"/>
       <c r="G14" s="161" t="s">
@@ -3751,7 +3751,7 @@
       <c r="I14" s="162"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="169"/>
       <c r="C15" s="4"/>
       <c r="D15" s="161" t="s">
@@ -3763,14 +3763,14 @@
       <c r="I15" s="166"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="169"/>
       <c r="C16" s="4"/>
       <c r="D16" s="163"/>
       <c r="E16" s="164"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="169"/>
       <c r="C17" s="4"/>
       <c r="D17" s="163"/>
@@ -3782,7 +3782,7 @@
       <c r="I17" s="162"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="169"/>
       <c r="C18" s="4"/>
       <c r="D18" s="165"/>
@@ -3792,12 +3792,12 @@
       <c r="I18" s="166"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="169"/>
       <c r="C19" s="4"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="169"/>
       <c r="C20" s="4"/>
       <c r="G20" s="161" t="s">
@@ -3807,7 +3807,7 @@
       <c r="I20" s="162"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="169"/>
       <c r="C21" s="4"/>
       <c r="D21" s="161" t="s">
@@ -3819,14 +3819,14 @@
       <c r="I21" s="166"/>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="169"/>
       <c r="C22" s="4"/>
       <c r="D22" s="163"/>
       <c r="E22" s="164"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="169"/>
       <c r="C23" s="4"/>
       <c r="D23" s="163"/>
@@ -3838,7 +3838,7 @@
       <c r="I23" s="162"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="169"/>
       <c r="C24" s="4"/>
       <c r="D24" s="165"/>
@@ -3848,12 +3848,12 @@
       <c r="I24" s="166"/>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="169"/>
       <c r="C25" s="4"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="169"/>
       <c r="C26" s="4"/>
       <c r="G26" s="161" t="s">
@@ -3863,7 +3863,7 @@
       <c r="I26" s="162"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="169"/>
       <c r="C27" s="4"/>
       <c r="D27" s="170" t="s">
@@ -3874,13 +3874,13 @@
       <c r="I27" s="166"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="169"/>
       <c r="C28" s="4"/>
       <c r="D28" s="171"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="169"/>
       <c r="C29" s="4"/>
       <c r="D29" s="171"/>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="169"/>
       <c r="C30" s="4"/>
       <c r="D30" s="172"/>
@@ -3902,7 +3902,7 @@
       <c r="I30" s="171"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="169"/>
       <c r="C31" s="4"/>
       <c r="F31" s="163"/>
@@ -3910,7 +3910,7 @@
       <c r="I31" s="171"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="169"/>
       <c r="C32" s="4"/>
       <c r="F32" s="165"/>
@@ -3918,12 +3918,12 @@
       <c r="I32" s="172"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="169"/>
       <c r="C33" s="4"/>
       <c r="J33" s="5"/>
     </row>
-    <row r="34" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="169"/>
       <c r="C34" s="4"/>
       <c r="E34" s="6"/>
@@ -3933,22 +3933,23 @@
       <c r="I34" s="6"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C35" s="161" t="s">
         <v>0</v>
       </c>
       <c r="D35" s="162"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C36" s="163"/>
       <c r="D36" s="164"/>
     </row>
-    <row r="37" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C37" s="165"/>
       <c r="D37" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D10:E13"/>
     <mergeCell ref="D5:E8"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="C35:D37"/>
@@ -3965,7 +3966,6 @@
     <mergeCell ref="G11:I12"/>
     <mergeCell ref="D21:E24"/>
     <mergeCell ref="D15:E18"/>
-    <mergeCell ref="D10:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3974,9 +3974,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F13F396-F96A-49EA-8021-E32953AD928A}">
   <dimension ref="B5:AS12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="2:45" ht="160.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:45" ht="160.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="175" t="s">
         <v>17</v>
       </c>
@@ -4024,12 +4024,12 @@
       <c r="AR5" s="176"/>
       <c r="AS5" s="176"/>
     </row>
-    <row r="10" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:45" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4049,42 +4049,42 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00D0565-200F-4204-914E-EAF3B8F03BFD}">
   <dimension ref="B2:AR29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="54" width="4.6640625" customWidth="1"/>
+    <col min="1" max="54" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:44" x14ac:dyDescent="0.3">
-      <c r="B2" s="192" t="s">
+    <row r="2" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B2" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="192"/>
-      <c r="K2" s="192"/>
-      <c r="L2" s="192"/>
-      <c r="M2" s="192"/>
-      <c r="N2" s="192"/>
-      <c r="O2" s="192"/>
-      <c r="P2" s="192"/>
-      <c r="Q2" s="192"/>
-      <c r="R2" s="192"/>
-      <c r="S2" s="192"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="192"/>
-      <c r="W2" s="192"/>
-      <c r="X2" s="192"/>
-      <c r="Y2" s="192"/>
-      <c r="Z2" s="192"/>
-      <c r="AA2" s="192"/>
-    </row>
-    <row r="4" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="C2" s="181"/>
+      <c r="D2" s="181"/>
+      <c r="E2" s="181"/>
+      <c r="F2" s="181"/>
+      <c r="G2" s="181"/>
+      <c r="H2" s="181"/>
+      <c r="I2" s="181"/>
+      <c r="J2" s="181"/>
+      <c r="K2" s="181"/>
+      <c r="L2" s="181"/>
+      <c r="M2" s="181"/>
+      <c r="N2" s="181"/>
+      <c r="O2" s="181"/>
+      <c r="P2" s="181"/>
+      <c r="Q2" s="181"/>
+      <c r="R2" s="181"/>
+      <c r="S2" s="181"/>
+      <c r="T2" s="181"/>
+      <c r="U2" s="181"/>
+      <c r="V2" s="181"/>
+      <c r="W2" s="181"/>
+      <c r="X2" s="181"/>
+      <c r="Y2" s="181"/>
+      <c r="Z2" s="181"/>
+      <c r="AA2" s="181"/>
+    </row>
+    <row r="4" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -4112,26 +4112,26 @@
       <c r="Z4" s="10"/>
       <c r="AA4" s="11"/>
     </row>
-    <row r="5" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B5" s="12"/>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="185"/>
-      <c r="K5" s="183" t="s">
+      <c r="D5" s="187"/>
+      <c r="E5" s="187"/>
+      <c r="F5" s="187"/>
+      <c r="G5" s="187"/>
+      <c r="H5" s="187"/>
+      <c r="I5" s="188"/>
+      <c r="K5" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="184"/>
-      <c r="M5" s="184"/>
-      <c r="N5" s="184"/>
-      <c r="O5" s="184"/>
-      <c r="P5" s="184"/>
-      <c r="Q5" s="185"/>
+      <c r="L5" s="187"/>
+      <c r="M5" s="187"/>
+      <c r="N5" s="187"/>
+      <c r="O5" s="187"/>
+      <c r="P5" s="187"/>
+      <c r="Q5" s="188"/>
       <c r="S5" s="177"/>
       <c r="T5" s="178"/>
       <c r="U5" s="178"/>
@@ -4142,83 +4142,83 @@
       <c r="Z5" s="179"/>
       <c r="AA5" s="13"/>
     </row>
-    <row r="6" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B6" s="12"/>
       <c r="C6" s="189"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="116"/>
       <c r="I6" s="190"/>
       <c r="K6" s="189"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="116"/>
+      <c r="O6" s="116"/>
+      <c r="P6" s="116"/>
       <c r="Q6" s="190"/>
-      <c r="S6" s="180"/>
-      <c r="T6" s="181"/>
-      <c r="U6" s="181"/>
-      <c r="V6" s="181"/>
-      <c r="W6" s="181"/>
-      <c r="X6" s="181"/>
-      <c r="Y6" s="181"/>
-      <c r="Z6" s="182"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="184"/>
+      <c r="U6" s="184"/>
+      <c r="V6" s="184"/>
+      <c r="W6" s="184"/>
+      <c r="X6" s="184"/>
+      <c r="Y6" s="184"/>
+      <c r="Z6" s="185"/>
       <c r="AA6" s="13"/>
-      <c r="AK6" s="183" t="s">
+      <c r="AK6" s="186" t="s">
         <v>21</v>
       </c>
-      <c r="AL6" s="184"/>
-      <c r="AM6" s="184"/>
-      <c r="AN6" s="184"/>
-      <c r="AO6" s="184"/>
-      <c r="AP6" s="184"/>
-      <c r="AQ6" s="184"/>
-      <c r="AR6" s="185"/>
-    </row>
-    <row r="7" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AL6" s="187"/>
+      <c r="AM6" s="187"/>
+      <c r="AN6" s="187"/>
+      <c r="AO6" s="187"/>
+      <c r="AP6" s="187"/>
+      <c r="AQ6" s="187"/>
+      <c r="AR6" s="188"/>
+    </row>
+    <row r="7" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B7" s="12"/>
       <c r="C7" s="189"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
+      <c r="D7" s="116"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="116"/>
+      <c r="H7" s="116"/>
       <c r="I7" s="190"/>
       <c r="K7" s="189"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="41"/>
+      <c r="L7" s="116"/>
+      <c r="M7" s="116"/>
+      <c r="N7" s="116"/>
+      <c r="O7" s="116"/>
+      <c r="P7" s="116"/>
       <c r="Q7" s="190"/>
       <c r="AA7" s="13"/>
-      <c r="AK7" s="186"/>
-      <c r="AL7" s="187"/>
-      <c r="AM7" s="187"/>
-      <c r="AN7" s="187"/>
-      <c r="AO7" s="187"/>
-      <c r="AP7" s="187"/>
-      <c r="AQ7" s="187"/>
-      <c r="AR7" s="188"/>
-    </row>
-    <row r="8" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AK7" s="191"/>
+      <c r="AL7" s="192"/>
+      <c r="AM7" s="192"/>
+      <c r="AN7" s="192"/>
+      <c r="AO7" s="192"/>
+      <c r="AP7" s="192"/>
+      <c r="AQ7" s="192"/>
+      <c r="AR7" s="193"/>
+    </row>
+    <row r="8" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="189"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
+      <c r="D8" s="116"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
       <c r="I8" s="190"/>
       <c r="K8" s="189"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="116"/>
       <c r="Q8" s="190"/>
       <c r="S8" s="177"/>
       <c r="T8" s="178"/>
@@ -4230,67 +4230,67 @@
       <c r="Z8" s="179"/>
       <c r="AA8" s="13"/>
     </row>
-    <row r="9" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B9" s="12"/>
       <c r="C9" s="189"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
+      <c r="D9" s="116"/>
+      <c r="E9" s="116"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
       <c r="I9" s="190"/>
       <c r="K9" s="189"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="116"/>
       <c r="Q9" s="190"/>
-      <c r="S9" s="180"/>
-      <c r="T9" s="181"/>
-      <c r="U9" s="181"/>
-      <c r="V9" s="181"/>
-      <c r="W9" s="181"/>
-      <c r="X9" s="181"/>
-      <c r="Y9" s="181"/>
-      <c r="Z9" s="182"/>
+      <c r="S9" s="183"/>
+      <c r="T9" s="184"/>
+      <c r="U9" s="184"/>
+      <c r="V9" s="184"/>
+      <c r="W9" s="184"/>
+      <c r="X9" s="184"/>
+      <c r="Y9" s="184"/>
+      <c r="Z9" s="185"/>
       <c r="AA9" s="13"/>
-      <c r="AD9" s="183" t="s">
+      <c r="AD9" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="AE9" s="184"/>
-      <c r="AF9" s="184"/>
-      <c r="AG9" s="184"/>
-      <c r="AH9" s="184"/>
-      <c r="AI9" s="184"/>
-      <c r="AJ9" s="185"/>
-    </row>
-    <row r="10" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AE9" s="187"/>
+      <c r="AF9" s="187"/>
+      <c r="AG9" s="187"/>
+      <c r="AH9" s="187"/>
+      <c r="AI9" s="187"/>
+      <c r="AJ9" s="188"/>
+    </row>
+    <row r="10" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B10" s="12"/>
-      <c r="C10" s="186"/>
-      <c r="D10" s="187"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="187"/>
-      <c r="H10" s="187"/>
-      <c r="I10" s="188"/>
-      <c r="K10" s="186"/>
-      <c r="L10" s="187"/>
-      <c r="M10" s="187"/>
-      <c r="N10" s="187"/>
-      <c r="O10" s="187"/>
-      <c r="P10" s="187"/>
-      <c r="Q10" s="188"/>
+      <c r="C10" s="191"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193"/>
+      <c r="K10" s="191"/>
+      <c r="L10" s="192"/>
+      <c r="M10" s="192"/>
+      <c r="N10" s="192"/>
+      <c r="O10" s="192"/>
+      <c r="P10" s="192"/>
+      <c r="Q10" s="193"/>
       <c r="AA10" s="13"/>
       <c r="AD10" s="189"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="41"/>
-      <c r="AG10" s="41"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="41"/>
+      <c r="AE10" s="116"/>
+      <c r="AF10" s="116"/>
+      <c r="AG10" s="116"/>
+      <c r="AH10" s="116"/>
+      <c r="AI10" s="116"/>
       <c r="AJ10" s="190"/>
     </row>
-    <row r="11" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B11" s="12"/>
       <c r="S11" s="177"/>
       <c r="T11" s="178"/>
@@ -4302,90 +4302,90 @@
       <c r="Z11" s="179"/>
       <c r="AA11" s="13"/>
       <c r="AD11" s="189"/>
-      <c r="AE11" s="41"/>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="41"/>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="41"/>
+      <c r="AE11" s="116"/>
+      <c r="AF11" s="116"/>
+      <c r="AG11" s="116"/>
+      <c r="AH11" s="116"/>
+      <c r="AI11" s="116"/>
       <c r="AJ11" s="190"/>
     </row>
-    <row r="12" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B12" s="12"/>
-      <c r="C12" s="183" t="s">
+      <c r="C12" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="185"/>
-      <c r="K12" s="183" t="s">
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="188"/>
+      <c r="K12" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="184"/>
-      <c r="M12" s="184"/>
-      <c r="N12" s="184"/>
-      <c r="O12" s="184"/>
-      <c r="P12" s="184"/>
-      <c r="Q12" s="185"/>
-      <c r="S12" s="180"/>
-      <c r="T12" s="181"/>
-      <c r="U12" s="181"/>
-      <c r="V12" s="181"/>
-      <c r="W12" s="181"/>
-      <c r="X12" s="181"/>
-      <c r="Y12" s="181"/>
-      <c r="Z12" s="182"/>
+      <c r="L12" s="187"/>
+      <c r="M12" s="187"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="187"/>
+      <c r="P12" s="187"/>
+      <c r="Q12" s="188"/>
+      <c r="S12" s="183"/>
+      <c r="T12" s="184"/>
+      <c r="U12" s="184"/>
+      <c r="V12" s="184"/>
+      <c r="W12" s="184"/>
+      <c r="X12" s="184"/>
+      <c r="Y12" s="184"/>
+      <c r="Z12" s="185"/>
       <c r="AA12" s="13"/>
       <c r="AD12" s="189"/>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="41"/>
-      <c r="AG12" s="41"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="41"/>
+      <c r="AE12" s="116"/>
+      <c r="AF12" s="116"/>
+      <c r="AG12" s="116"/>
+      <c r="AH12" s="116"/>
+      <c r="AI12" s="116"/>
       <c r="AJ12" s="190"/>
     </row>
-    <row r="13" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B13" s="12"/>
       <c r="C13" s="189"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
       <c r="I13" s="190"/>
       <c r="K13" s="189"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="116"/>
+      <c r="N13" s="116"/>
+      <c r="O13" s="116"/>
+      <c r="P13" s="116"/>
       <c r="Q13" s="190"/>
       <c r="AA13" s="13"/>
       <c r="AD13" s="189"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="41"/>
-      <c r="AG13" s="41"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="41"/>
+      <c r="AE13" s="116"/>
+      <c r="AF13" s="116"/>
+      <c r="AG13" s="116"/>
+      <c r="AH13" s="116"/>
+      <c r="AI13" s="116"/>
       <c r="AJ13" s="190"/>
     </row>
-    <row r="14" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B14" s="12"/>
       <c r="C14" s="189"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
       <c r="I14" s="190"/>
       <c r="K14" s="189"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
+      <c r="L14" s="116"/>
+      <c r="M14" s="116"/>
+      <c r="N14" s="116"/>
+      <c r="O14" s="116"/>
+      <c r="P14" s="116"/>
       <c r="Q14" s="190"/>
       <c r="S14" s="177"/>
       <c r="T14" s="178"/>
@@ -4396,55 +4396,55 @@
       <c r="Y14" s="178"/>
       <c r="Z14" s="179"/>
       <c r="AA14" s="13"/>
-      <c r="AD14" s="186"/>
-      <c r="AE14" s="187"/>
-      <c r="AF14" s="187"/>
-      <c r="AG14" s="187"/>
-      <c r="AH14" s="187"/>
-      <c r="AI14" s="187"/>
-      <c r="AJ14" s="188"/>
-    </row>
-    <row r="15" spans="2:44" x14ac:dyDescent="0.3">
+      <c r="AD14" s="191"/>
+      <c r="AE14" s="192"/>
+      <c r="AF14" s="192"/>
+      <c r="AG14" s="192"/>
+      <c r="AH14" s="192"/>
+      <c r="AI14" s="192"/>
+      <c r="AJ14" s="193"/>
+    </row>
+    <row r="15" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B15" s="12"/>
       <c r="C15" s="189"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
       <c r="I15" s="190"/>
       <c r="K15" s="189"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
       <c r="Q15" s="190"/>
-      <c r="S15" s="180"/>
-      <c r="T15" s="181"/>
-      <c r="U15" s="181"/>
-      <c r="V15" s="181"/>
-      <c r="W15" s="181"/>
-      <c r="X15" s="181"/>
-      <c r="Y15" s="181"/>
-      <c r="Z15" s="182"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="184"/>
+      <c r="U15" s="184"/>
+      <c r="V15" s="184"/>
+      <c r="W15" s="184"/>
+      <c r="X15" s="184"/>
+      <c r="Y15" s="184"/>
+      <c r="Z15" s="185"/>
       <c r="AA15" s="13"/>
     </row>
-    <row r="16" spans="2:44" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:44" x14ac:dyDescent="0.25">
       <c r="B16" s="12"/>
       <c r="C16" s="189"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
       <c r="I16" s="190"/>
       <c r="K16" s="189"/>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
+      <c r="L16" s="116"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="116"/>
+      <c r="O16" s="116"/>
+      <c r="P16" s="116"/>
       <c r="Q16" s="190"/>
       <c r="AA16" s="13"/>
       <c r="AD16" s="177" t="s">
@@ -4456,22 +4456,22 @@
       <c r="AH16" s="178"/>
       <c r="AI16" s="179"/>
     </row>
-    <row r="17" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B17" s="12"/>
-      <c r="C17" s="186"/>
-      <c r="D17" s="187"/>
-      <c r="E17" s="187"/>
-      <c r="F17" s="187"/>
-      <c r="G17" s="187"/>
-      <c r="H17" s="187"/>
-      <c r="I17" s="188"/>
-      <c r="K17" s="186"/>
-      <c r="L17" s="187"/>
-      <c r="M17" s="187"/>
-      <c r="N17" s="187"/>
-      <c r="O17" s="187"/>
-      <c r="P17" s="187"/>
-      <c r="Q17" s="188"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="192"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="192"/>
+      <c r="G17" s="192"/>
+      <c r="H17" s="192"/>
+      <c r="I17" s="193"/>
+      <c r="K17" s="191"/>
+      <c r="L17" s="192"/>
+      <c r="M17" s="192"/>
+      <c r="N17" s="192"/>
+      <c r="O17" s="192"/>
+      <c r="P17" s="192"/>
+      <c r="Q17" s="193"/>
       <c r="S17" s="177"/>
       <c r="T17" s="178"/>
       <c r="U17" s="178"/>
@@ -4481,42 +4481,42 @@
       <c r="Y17" s="178"/>
       <c r="Z17" s="179"/>
       <c r="AA17" s="13"/>
-      <c r="AD17" s="191"/>
-      <c r="AE17" s="192"/>
-      <c r="AF17" s="192"/>
-      <c r="AG17" s="192"/>
-      <c r="AH17" s="192"/>
-      <c r="AI17" s="193"/>
-    </row>
-    <row r="18" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD17" s="180"/>
+      <c r="AE17" s="181"/>
+      <c r="AF17" s="181"/>
+      <c r="AG17" s="181"/>
+      <c r="AH17" s="181"/>
+      <c r="AI17" s="182"/>
+    </row>
+    <row r="18" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B18" s="12"/>
-      <c r="S18" s="180"/>
-      <c r="T18" s="181"/>
-      <c r="U18" s="181"/>
-      <c r="V18" s="181"/>
-      <c r="W18" s="181"/>
-      <c r="X18" s="181"/>
-      <c r="Y18" s="181"/>
-      <c r="Z18" s="182"/>
+      <c r="S18" s="183"/>
+      <c r="T18" s="184"/>
+      <c r="U18" s="184"/>
+      <c r="V18" s="184"/>
+      <c r="W18" s="184"/>
+      <c r="X18" s="184"/>
+      <c r="Y18" s="184"/>
+      <c r="Z18" s="185"/>
       <c r="AA18" s="13"/>
-      <c r="AD18" s="191"/>
-      <c r="AE18" s="192"/>
-      <c r="AF18" s="192"/>
-      <c r="AG18" s="192"/>
-      <c r="AH18" s="192"/>
-      <c r="AI18" s="193"/>
-    </row>
-    <row r="19" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD18" s="180"/>
+      <c r="AE18" s="181"/>
+      <c r="AF18" s="181"/>
+      <c r="AG18" s="181"/>
+      <c r="AH18" s="181"/>
+      <c r="AI18" s="182"/>
+    </row>
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B19" s="12"/>
       <c r="AA19" s="13"/>
-      <c r="AD19" s="191"/>
-      <c r="AE19" s="192"/>
-      <c r="AF19" s="192"/>
-      <c r="AG19" s="192"/>
-      <c r="AH19" s="192"/>
-      <c r="AI19" s="193"/>
-    </row>
-    <row r="20" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD19" s="180"/>
+      <c r="AE19" s="181"/>
+      <c r="AF19" s="181"/>
+      <c r="AG19" s="181"/>
+      <c r="AH19" s="181"/>
+      <c r="AI19" s="182"/>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B20" s="12"/>
       <c r="S20" s="177"/>
       <c r="T20" s="178"/>
@@ -4527,14 +4527,14 @@
       <c r="Y20" s="178"/>
       <c r="Z20" s="179"/>
       <c r="AA20" s="13"/>
-      <c r="AD20" s="191"/>
-      <c r="AE20" s="192"/>
-      <c r="AF20" s="192"/>
-      <c r="AG20" s="192"/>
-      <c r="AH20" s="192"/>
-      <c r="AI20" s="193"/>
-    </row>
-    <row r="21" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD20" s="180"/>
+      <c r="AE20" s="181"/>
+      <c r="AF20" s="181"/>
+      <c r="AG20" s="181"/>
+      <c r="AH20" s="181"/>
+      <c r="AI20" s="182"/>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B21" s="12"/>
       <c r="C21" s="177" t="s">
         <v>22</v>
@@ -4544,46 +4544,46 @@
       <c r="F21" s="178"/>
       <c r="G21" s="178"/>
       <c r="H21" s="179"/>
-      <c r="S21" s="180"/>
-      <c r="T21" s="181"/>
-      <c r="U21" s="181"/>
-      <c r="V21" s="181"/>
-      <c r="W21" s="181"/>
-      <c r="X21" s="181"/>
-      <c r="Y21" s="181"/>
-      <c r="Z21" s="182"/>
+      <c r="S21" s="183"/>
+      <c r="T21" s="184"/>
+      <c r="U21" s="184"/>
+      <c r="V21" s="184"/>
+      <c r="W21" s="184"/>
+      <c r="X21" s="184"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="185"/>
       <c r="AA21" s="13"/>
-      <c r="AD21" s="191"/>
-      <c r="AE21" s="192"/>
-      <c r="AF21" s="192"/>
-      <c r="AG21" s="192"/>
-      <c r="AH21" s="192"/>
-      <c r="AI21" s="193"/>
-    </row>
-    <row r="22" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD21" s="180"/>
+      <c r="AE21" s="181"/>
+      <c r="AF21" s="181"/>
+      <c r="AG21" s="181"/>
+      <c r="AH21" s="181"/>
+      <c r="AI21" s="182"/>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B22" s="12"/>
-      <c r="C22" s="191"/>
-      <c r="D22" s="192"/>
-      <c r="E22" s="192"/>
-      <c r="F22" s="192"/>
-      <c r="G22" s="192"/>
-      <c r="H22" s="193"/>
+      <c r="C22" s="180"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="182"/>
       <c r="AA22" s="13"/>
-      <c r="AD22" s="180"/>
-      <c r="AE22" s="181"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="181"/>
-      <c r="AH22" s="181"/>
-      <c r="AI22" s="182"/>
-    </row>
-    <row r="23" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="AD22" s="183"/>
+      <c r="AE22" s="184"/>
+      <c r="AF22" s="184"/>
+      <c r="AG22" s="184"/>
+      <c r="AH22" s="184"/>
+      <c r="AI22" s="185"/>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B23" s="12"/>
-      <c r="C23" s="191"/>
-      <c r="D23" s="192"/>
-      <c r="E23" s="192"/>
-      <c r="F23" s="192"/>
-      <c r="G23" s="192"/>
-      <c r="H23" s="193"/>
+      <c r="C23" s="180"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="181"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="182"/>
       <c r="S23" s="177"/>
       <c r="T23" s="178"/>
       <c r="U23" s="178"/>
@@ -4594,42 +4594,42 @@
       <c r="Z23" s="179"/>
       <c r="AA23" s="13"/>
     </row>
-    <row r="24" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B24" s="12"/>
-      <c r="C24" s="191"/>
-      <c r="D24" s="192"/>
-      <c r="E24" s="192"/>
-      <c r="F24" s="192"/>
-      <c r="G24" s="192"/>
-      <c r="H24" s="193"/>
-      <c r="S24" s="180"/>
-      <c r="T24" s="181"/>
-      <c r="U24" s="181"/>
-      <c r="V24" s="181"/>
-      <c r="W24" s="181"/>
-      <c r="X24" s="181"/>
-      <c r="Y24" s="181"/>
-      <c r="Z24" s="182"/>
+      <c r="C24" s="180"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="182"/>
+      <c r="S24" s="183"/>
+      <c r="T24" s="184"/>
+      <c r="U24" s="184"/>
+      <c r="V24" s="184"/>
+      <c r="W24" s="184"/>
+      <c r="X24" s="184"/>
+      <c r="Y24" s="184"/>
+      <c r="Z24" s="185"/>
       <c r="AA24" s="13"/>
     </row>
-    <row r="25" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B25" s="12"/>
-      <c r="C25" s="191"/>
-      <c r="D25" s="192"/>
-      <c r="E25" s="192"/>
-      <c r="F25" s="192"/>
-      <c r="G25" s="192"/>
-      <c r="H25" s="193"/>
+      <c r="C25" s="180"/>
+      <c r="D25" s="181"/>
+      <c r="E25" s="181"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="182"/>
       <c r="AA25" s="13"/>
     </row>
-    <row r="26" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B26" s="12"/>
-      <c r="C26" s="191"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="192"/>
-      <c r="G26" s="192"/>
-      <c r="H26" s="193"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="182"/>
       <c r="S26" s="177"/>
       <c r="T26" s="178"/>
       <c r="U26" s="178"/>
@@ -4640,29 +4640,29 @@
       <c r="Z26" s="179"/>
       <c r="AA26" s="13"/>
     </row>
-    <row r="27" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B27" s="12"/>
-      <c r="C27" s="180"/>
-      <c r="D27" s="181"/>
-      <c r="E27" s="181"/>
-      <c r="F27" s="181"/>
-      <c r="G27" s="181"/>
-      <c r="H27" s="182"/>
-      <c r="S27" s="180"/>
-      <c r="T27" s="181"/>
-      <c r="U27" s="181"/>
-      <c r="V27" s="181"/>
-      <c r="W27" s="181"/>
-      <c r="X27" s="181"/>
-      <c r="Y27" s="181"/>
-      <c r="Z27" s="182"/>
+      <c r="C27" s="183"/>
+      <c r="D27" s="184"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="184"/>
+      <c r="G27" s="184"/>
+      <c r="H27" s="185"/>
+      <c r="S27" s="183"/>
+      <c r="T27" s="184"/>
+      <c r="U27" s="184"/>
+      <c r="V27" s="184"/>
+      <c r="W27" s="184"/>
+      <c r="X27" s="184"/>
+      <c r="Y27" s="184"/>
+      <c r="Z27" s="185"/>
       <c r="AA27" s="13"/>
     </row>
-    <row r="28" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B28" s="12"/>
       <c r="AA28" s="13"/>
     </row>
-    <row r="29" spans="2:35" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
       <c r="B29" s="14"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
@@ -4692,23 +4692,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AK6:AR7"/>
+    <mergeCell ref="AD9:AJ14"/>
+    <mergeCell ref="AD16:AI22"/>
+    <mergeCell ref="S17:Z18"/>
+    <mergeCell ref="B2:AA2"/>
+    <mergeCell ref="S5:Z6"/>
+    <mergeCell ref="S8:Z9"/>
+    <mergeCell ref="S11:Z12"/>
+    <mergeCell ref="S14:Z15"/>
     <mergeCell ref="C21:H27"/>
     <mergeCell ref="S23:Z24"/>
     <mergeCell ref="K5:Q10"/>
     <mergeCell ref="C5:I10"/>
     <mergeCell ref="K12:Q17"/>
     <mergeCell ref="C12:I17"/>
-    <mergeCell ref="B2:AA2"/>
-    <mergeCell ref="S5:Z6"/>
-    <mergeCell ref="S8:Z9"/>
-    <mergeCell ref="S11:Z12"/>
-    <mergeCell ref="S14:Z15"/>
     <mergeCell ref="S20:Z21"/>
     <mergeCell ref="S26:Z27"/>
-    <mergeCell ref="AK6:AR7"/>
-    <mergeCell ref="AD9:AJ14"/>
-    <mergeCell ref="AD16:AI22"/>
-    <mergeCell ref="S17:Z18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4717,55 +4717,55 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F57F5BB-342A-4909-9182-1EA44E81E058}">
   <dimension ref="B2:BP85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="3" max="21" width="4.6640625" customWidth="1"/>
-    <col min="22" max="22" width="3.6640625" customWidth="1"/>
-    <col min="23" max="23" width="4.6640625" customWidth="1"/>
-    <col min="24" max="24" width="5.6640625" customWidth="1"/>
-    <col min="25" max="26" width="4.6640625" customWidth="1"/>
-    <col min="27" max="27" width="5.6640625" customWidth="1"/>
-    <col min="28" max="29" width="4.6640625" customWidth="1"/>
-    <col min="30" max="30" width="5.88671875" customWidth="1"/>
-    <col min="31" max="33" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="21" width="4.7109375" customWidth="1"/>
+    <col min="22" max="22" width="3.7109375" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" customWidth="1"/>
+    <col min="25" max="26" width="4.7109375" customWidth="1"/>
+    <col min="27" max="27" width="5.7109375" customWidth="1"/>
+    <col min="28" max="29" width="4.7109375" customWidth="1"/>
+    <col min="30" max="30" width="5.85546875" customWidth="1"/>
+    <col min="31" max="33" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:31" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="D2" s="194" t="s">
+    <row r="2" spans="2:31" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="D2" s="253" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="195"/>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="195"/>
-      <c r="I2" s="195"/>
-      <c r="J2" s="195"/>
-      <c r="K2" s="195"/>
-      <c r="L2" s="195"/>
-      <c r="M2" s="195"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="195"/>
-      <c r="P2" s="195"/>
-      <c r="Q2" s="195"/>
-      <c r="R2" s="195"/>
-      <c r="S2" s="195"/>
-      <c r="T2" s="195"/>
-      <c r="U2" s="195"/>
-      <c r="V2" s="195"/>
-      <c r="W2" s="195"/>
-      <c r="X2" s="195"/>
-      <c r="Y2" s="195"/>
-      <c r="Z2" s="195"/>
-      <c r="AA2" s="195"/>
-      <c r="AB2" s="195"/>
-      <c r="AC2" s="195"/>
-      <c r="AD2" s="195"/>
-      <c r="AE2" s="196"/>
-    </row>
-    <row r="4" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B4" s="131" t="s">
+      <c r="E2" s="254"/>
+      <c r="F2" s="254"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="254"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="254"/>
+      <c r="N2" s="254"/>
+      <c r="O2" s="254"/>
+      <c r="P2" s="254"/>
+      <c r="Q2" s="254"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="254"/>
+      <c r="U2" s="254"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="254"/>
+      <c r="X2" s="254"/>
+      <c r="Y2" s="254"/>
+      <c r="Z2" s="254"/>
+      <c r="AA2" s="254"/>
+      <c r="AB2" s="254"/>
+      <c r="AC2" s="254"/>
+      <c r="AD2" s="254"/>
+      <c r="AE2" s="255"/>
+    </row>
+    <row r="4" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B4" s="41" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="17"/>
@@ -4797,8 +4797,8 @@
       <c r="AD4" s="18"/>
       <c r="AE4" s="19"/>
     </row>
-    <row r="5" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B5" s="132"/>
+    <row r="5" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B5" s="42"/>
       <c r="D5" s="20"/>
       <c r="E5" s="212" t="s">
         <v>24</v>
@@ -4823,19 +4823,19 @@
       <c r="U5" s="21"/>
       <c r="V5" s="21"/>
       <c r="W5" s="21"/>
-      <c r="X5" s="203" t="s">
+      <c r="X5" s="256" t="s">
         <v>26</v>
       </c>
-      <c r="Y5" s="204"/>
-      <c r="Z5" s="204"/>
-      <c r="AA5" s="204"/>
-      <c r="AB5" s="204"/>
-      <c r="AC5" s="204"/>
-      <c r="AD5" s="205"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
+      <c r="AA5" s="257"/>
+      <c r="AB5" s="257"/>
+      <c r="AC5" s="257"/>
+      <c r="AD5" s="258"/>
       <c r="AE5" s="22"/>
     </row>
-    <row r="6" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B6" s="132"/>
+    <row r="6" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B6" s="42"/>
       <c r="D6" s="20"/>
       <c r="E6" s="215"/>
       <c r="F6" s="216"/>
@@ -4856,17 +4856,17 @@
       <c r="U6" s="21"/>
       <c r="V6" s="21"/>
       <c r="W6" s="21"/>
-      <c r="X6" s="206"/>
-      <c r="Y6" s="207"/>
-      <c r="Z6" s="207"/>
-      <c r="AA6" s="207"/>
-      <c r="AB6" s="207"/>
-      <c r="AC6" s="207"/>
-      <c r="AD6" s="208"/>
+      <c r="X6" s="259"/>
+      <c r="Y6" s="260"/>
+      <c r="Z6" s="260"/>
+      <c r="AA6" s="260"/>
+      <c r="AB6" s="260"/>
+      <c r="AC6" s="260"/>
+      <c r="AD6" s="261"/>
       <c r="AE6" s="22"/>
     </row>
-    <row r="7" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="132"/>
+    <row r="7" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B7" s="42"/>
       <c r="D7" s="20"/>
       <c r="E7" s="215"/>
       <c r="F7" s="216"/>
@@ -4887,17 +4887,17 @@
       <c r="U7" s="21"/>
       <c r="V7" s="21"/>
       <c r="W7" s="21"/>
-      <c r="X7" s="206"/>
-      <c r="Y7" s="207"/>
-      <c r="Z7" s="207"/>
-      <c r="AA7" s="207"/>
-      <c r="AB7" s="207"/>
-      <c r="AC7" s="207"/>
-      <c r="AD7" s="208"/>
+      <c r="X7" s="259"/>
+      <c r="Y7" s="260"/>
+      <c r="Z7" s="260"/>
+      <c r="AA7" s="260"/>
+      <c r="AB7" s="260"/>
+      <c r="AC7" s="260"/>
+      <c r="AD7" s="261"/>
       <c r="AE7" s="22"/>
     </row>
-    <row r="8" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="132"/>
+    <row r="8" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="42"/>
       <c r="D8" s="20"/>
       <c r="E8" s="215"/>
       <c r="F8" s="216"/>
@@ -4918,17 +4918,17 @@
       <c r="U8" s="21"/>
       <c r="V8" s="21"/>
       <c r="W8" s="21"/>
-      <c r="X8" s="206"/>
-      <c r="Y8" s="207"/>
-      <c r="Z8" s="207"/>
-      <c r="AA8" s="207"/>
-      <c r="AB8" s="207"/>
-      <c r="AC8" s="207"/>
-      <c r="AD8" s="208"/>
+      <c r="X8" s="259"/>
+      <c r="Y8" s="260"/>
+      <c r="Z8" s="260"/>
+      <c r="AA8" s="260"/>
+      <c r="AB8" s="260"/>
+      <c r="AC8" s="260"/>
+      <c r="AD8" s="261"/>
       <c r="AE8" s="22"/>
     </row>
-    <row r="9" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B9" s="132"/>
+    <row r="9" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="42"/>
       <c r="D9" s="20"/>
       <c r="E9" s="215"/>
       <c r="F9" s="216"/>
@@ -4949,17 +4949,17 @@
       <c r="U9" s="21"/>
       <c r="V9" s="21"/>
       <c r="W9" s="21"/>
-      <c r="X9" s="209"/>
-      <c r="Y9" s="210"/>
-      <c r="Z9" s="210"/>
-      <c r="AA9" s="210"/>
-      <c r="AB9" s="210"/>
-      <c r="AC9" s="210"/>
-      <c r="AD9" s="211"/>
+      <c r="X9" s="262"/>
+      <c r="Y9" s="263"/>
+      <c r="Z9" s="263"/>
+      <c r="AA9" s="263"/>
+      <c r="AB9" s="263"/>
+      <c r="AC9" s="263"/>
+      <c r="AD9" s="264"/>
       <c r="AE9" s="22"/>
     </row>
-    <row r="10" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="132"/>
+    <row r="10" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="42"/>
       <c r="D10" s="20"/>
       <c r="E10" s="215"/>
       <c r="F10" s="216"/>
@@ -4989,8 +4989,8 @@
       <c r="AD10" s="21"/>
       <c r="AE10" s="22"/>
     </row>
-    <row r="11" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B11" s="132"/>
+    <row r="11" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="42"/>
       <c r="D11" s="20"/>
       <c r="E11" s="218"/>
       <c r="F11" s="219"/>
@@ -5020,8 +5020,8 @@
       <c r="AD11" s="21"/>
       <c r="AE11" s="22"/>
     </row>
-    <row r="12" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="132"/>
+    <row r="12" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="42"/>
       <c r="D12" s="20"/>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
@@ -5041,24 +5041,24 @@
       <c r="T12" s="21"/>
       <c r="U12" s="21"/>
       <c r="V12" s="21"/>
-      <c r="W12" s="197" t="s">
+      <c r="W12" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="X12" s="198"/>
+      <c r="X12" s="195"/>
       <c r="Y12" s="37"/>
-      <c r="Z12" s="197" t="s">
+      <c r="Z12" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AA12" s="198"/>
+      <c r="AA12" s="195"/>
       <c r="AB12" s="37"/>
-      <c r="AC12" s="197" t="s">
+      <c r="AC12" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AD12" s="198"/>
+      <c r="AD12" s="195"/>
       <c r="AE12" s="22"/>
     </row>
-    <row r="13" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B13" s="132"/>
+    <row r="13" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="42"/>
       <c r="D13" s="20"/>
       <c r="E13" s="212" t="s">
         <v>24</v>
@@ -5082,18 +5082,18 @@
       <c r="T13" s="21"/>
       <c r="U13" s="21"/>
       <c r="V13" s="21"/>
-      <c r="W13" s="199"/>
-      <c r="X13" s="200"/>
+      <c r="W13" s="196"/>
+      <c r="X13" s="197"/>
       <c r="Y13" s="37"/>
-      <c r="Z13" s="199"/>
-      <c r="AA13" s="200"/>
+      <c r="Z13" s="196"/>
+      <c r="AA13" s="197"/>
       <c r="AB13" s="37"/>
-      <c r="AC13" s="199"/>
-      <c r="AD13" s="200"/>
+      <c r="AC13" s="196"/>
+      <c r="AD13" s="197"/>
       <c r="AE13" s="22"/>
     </row>
-    <row r="14" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B14" s="132"/>
+    <row r="14" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="42"/>
       <c r="D14" s="20"/>
       <c r="E14" s="215"/>
       <c r="F14" s="216"/>
@@ -5113,18 +5113,18 @@
       <c r="T14" s="21"/>
       <c r="U14" s="21"/>
       <c r="V14" s="21"/>
-      <c r="W14" s="199"/>
-      <c r="X14" s="200"/>
+      <c r="W14" s="196"/>
+      <c r="X14" s="197"/>
       <c r="Y14" s="37"/>
-      <c r="Z14" s="199"/>
-      <c r="AA14" s="200"/>
+      <c r="Z14" s="196"/>
+      <c r="AA14" s="197"/>
       <c r="AB14" s="37"/>
-      <c r="AC14" s="199"/>
-      <c r="AD14" s="200"/>
+      <c r="AC14" s="196"/>
+      <c r="AD14" s="197"/>
       <c r="AE14" s="22"/>
     </row>
-    <row r="15" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B15" s="132"/>
+    <row r="15" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="42"/>
       <c r="D15" s="20"/>
       <c r="E15" s="215"/>
       <c r="F15" s="216"/>
@@ -5144,18 +5144,18 @@
       <c r="T15" s="21"/>
       <c r="U15" s="21"/>
       <c r="V15" s="21"/>
-      <c r="W15" s="199"/>
-      <c r="X15" s="200"/>
+      <c r="W15" s="196"/>
+      <c r="X15" s="197"/>
       <c r="Y15" s="37"/>
-      <c r="Z15" s="199"/>
-      <c r="AA15" s="200"/>
+      <c r="Z15" s="196"/>
+      <c r="AA15" s="197"/>
       <c r="AB15" s="37"/>
-      <c r="AC15" s="199"/>
-      <c r="AD15" s="200"/>
+      <c r="AC15" s="196"/>
+      <c r="AD15" s="197"/>
       <c r="AE15" s="22"/>
     </row>
-    <row r="16" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B16" s="132"/>
+    <row r="16" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="42"/>
       <c r="D16" s="20"/>
       <c r="E16" s="215"/>
       <c r="F16" s="216"/>
@@ -5175,18 +5175,18 @@
       <c r="T16" s="21"/>
       <c r="U16" s="21"/>
       <c r="V16" s="21"/>
-      <c r="W16" s="199"/>
-      <c r="X16" s="200"/>
+      <c r="W16" s="196"/>
+      <c r="X16" s="197"/>
       <c r="Y16" s="37"/>
-      <c r="Z16" s="199"/>
-      <c r="AA16" s="200"/>
+      <c r="Z16" s="196"/>
+      <c r="AA16" s="197"/>
       <c r="AB16" s="37"/>
-      <c r="AC16" s="199"/>
-      <c r="AD16" s="200"/>
+      <c r="AC16" s="196"/>
+      <c r="AD16" s="197"/>
       <c r="AE16" s="22"/>
     </row>
-    <row r="17" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B17" s="132"/>
+    <row r="17" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="42"/>
       <c r="D17" s="20"/>
       <c r="E17" s="215"/>
       <c r="F17" s="216"/>
@@ -5206,18 +5206,18 @@
       <c r="T17" s="21"/>
       <c r="U17" s="21"/>
       <c r="V17" s="21"/>
-      <c r="W17" s="199"/>
-      <c r="X17" s="200"/>
+      <c r="W17" s="196"/>
+      <c r="X17" s="197"/>
       <c r="Y17" s="37"/>
-      <c r="Z17" s="199"/>
-      <c r="AA17" s="200"/>
+      <c r="Z17" s="196"/>
+      <c r="AA17" s="197"/>
       <c r="AB17" s="37"/>
-      <c r="AC17" s="199"/>
-      <c r="AD17" s="200"/>
+      <c r="AC17" s="196"/>
+      <c r="AD17" s="197"/>
       <c r="AE17" s="22"/>
     </row>
-    <row r="18" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B18" s="132"/>
+    <row r="18" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="42"/>
       <c r="D18" s="20"/>
       <c r="E18" s="215"/>
       <c r="F18" s="216"/>
@@ -5237,18 +5237,18 @@
       <c r="T18" s="21"/>
       <c r="U18" s="21"/>
       <c r="V18" s="21"/>
-      <c r="W18" s="201"/>
-      <c r="X18" s="202"/>
+      <c r="W18" s="198"/>
+      <c r="X18" s="199"/>
       <c r="Y18" s="37"/>
-      <c r="Z18" s="201"/>
-      <c r="AA18" s="202"/>
+      <c r="Z18" s="198"/>
+      <c r="AA18" s="199"/>
       <c r="AB18" s="37"/>
-      <c r="AC18" s="201"/>
-      <c r="AD18" s="202"/>
+      <c r="AC18" s="198"/>
+      <c r="AD18" s="199"/>
       <c r="AE18" s="22"/>
     </row>
-    <row r="19" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B19" s="132"/>
+    <row r="19" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B19" s="42"/>
       <c r="D19" s="20"/>
       <c r="E19" s="218"/>
       <c r="F19" s="219"/>
@@ -5278,8 +5278,8 @@
       <c r="AD19" s="37"/>
       <c r="AE19" s="22"/>
     </row>
-    <row r="20" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="132"/>
+    <row r="20" spans="2:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="42"/>
       <c r="D20" s="20"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -5299,24 +5299,24 @@
       <c r="T20" s="21"/>
       <c r="U20" s="21"/>
       <c r="V20" s="21"/>
-      <c r="W20" s="197" t="s">
+      <c r="W20" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="X20" s="198"/>
+      <c r="X20" s="195"/>
       <c r="Y20" s="37"/>
-      <c r="Z20" s="197" t="s">
+      <c r="Z20" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AA20" s="198"/>
+      <c r="AA20" s="195"/>
       <c r="AB20" s="37"/>
-      <c r="AC20" s="197" t="s">
+      <c r="AC20" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AD20" s="198"/>
+      <c r="AD20" s="195"/>
       <c r="AE20" s="22"/>
     </row>
-    <row r="21" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B21" s="132"/>
+    <row r="21" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="42"/>
       <c r="D21" s="20"/>
       <c r="E21" s="212" t="s">
         <v>24</v>
@@ -5340,18 +5340,18 @@
       <c r="T21" s="21"/>
       <c r="U21" s="21"/>
       <c r="V21" s="21"/>
-      <c r="W21" s="199"/>
-      <c r="X21" s="200"/>
+      <c r="W21" s="196"/>
+      <c r="X21" s="197"/>
       <c r="Y21" s="37"/>
-      <c r="Z21" s="199"/>
-      <c r="AA21" s="200"/>
+      <c r="Z21" s="196"/>
+      <c r="AA21" s="197"/>
       <c r="AB21" s="37"/>
-      <c r="AC21" s="199"/>
-      <c r="AD21" s="200"/>
+      <c r="AC21" s="196"/>
+      <c r="AD21" s="197"/>
       <c r="AE21" s="22"/>
     </row>
-    <row r="22" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B22" s="132"/>
+    <row r="22" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B22" s="42"/>
       <c r="D22" s="20"/>
       <c r="E22" s="215"/>
       <c r="F22" s="216"/>
@@ -5371,18 +5371,18 @@
       <c r="T22" s="21"/>
       <c r="U22" s="21"/>
       <c r="V22" s="21"/>
-      <c r="W22" s="199"/>
-      <c r="X22" s="200"/>
+      <c r="W22" s="196"/>
+      <c r="X22" s="197"/>
       <c r="Y22" s="37"/>
-      <c r="Z22" s="199"/>
-      <c r="AA22" s="200"/>
+      <c r="Z22" s="196"/>
+      <c r="AA22" s="197"/>
       <c r="AB22" s="37"/>
-      <c r="AC22" s="199"/>
-      <c r="AD22" s="200"/>
+      <c r="AC22" s="196"/>
+      <c r="AD22" s="197"/>
       <c r="AE22" s="22"/>
     </row>
-    <row r="23" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B23" s="132"/>
+    <row r="23" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="42"/>
       <c r="D23" s="20"/>
       <c r="E23" s="215"/>
       <c r="F23" s="216"/>
@@ -5402,18 +5402,18 @@
       <c r="T23" s="21"/>
       <c r="U23" s="21"/>
       <c r="V23" s="21"/>
-      <c r="W23" s="199"/>
-      <c r="X23" s="200"/>
+      <c r="W23" s="196"/>
+      <c r="X23" s="197"/>
       <c r="Y23" s="37"/>
-      <c r="Z23" s="199"/>
-      <c r="AA23" s="200"/>
+      <c r="Z23" s="196"/>
+      <c r="AA23" s="197"/>
       <c r="AB23" s="37"/>
-      <c r="AC23" s="199"/>
-      <c r="AD23" s="200"/>
+      <c r="AC23" s="196"/>
+      <c r="AD23" s="197"/>
       <c r="AE23" s="22"/>
     </row>
-    <row r="24" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B24" s="132"/>
+    <row r="24" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="42"/>
       <c r="D24" s="20"/>
       <c r="E24" s="215"/>
       <c r="F24" s="216"/>
@@ -5433,18 +5433,18 @@
       <c r="T24" s="21"/>
       <c r="U24" s="21"/>
       <c r="V24" s="21"/>
-      <c r="W24" s="199"/>
-      <c r="X24" s="200"/>
+      <c r="W24" s="196"/>
+      <c r="X24" s="197"/>
       <c r="Y24" s="37"/>
-      <c r="Z24" s="199"/>
-      <c r="AA24" s="200"/>
+      <c r="Z24" s="196"/>
+      <c r="AA24" s="197"/>
       <c r="AB24" s="37"/>
-      <c r="AC24" s="199"/>
-      <c r="AD24" s="200"/>
+      <c r="AC24" s="196"/>
+      <c r="AD24" s="197"/>
       <c r="AE24" s="22"/>
     </row>
-    <row r="25" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B25" s="132"/>
+    <row r="25" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="42"/>
       <c r="D25" s="20"/>
       <c r="E25" s="215"/>
       <c r="F25" s="216"/>
@@ -5464,18 +5464,18 @@
       <c r="T25" s="21"/>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
-      <c r="W25" s="199"/>
-      <c r="X25" s="200"/>
+      <c r="W25" s="196"/>
+      <c r="X25" s="197"/>
       <c r="Y25" s="37"/>
-      <c r="Z25" s="199"/>
-      <c r="AA25" s="200"/>
+      <c r="Z25" s="196"/>
+      <c r="AA25" s="197"/>
       <c r="AB25" s="37"/>
-      <c r="AC25" s="199"/>
-      <c r="AD25" s="200"/>
+      <c r="AC25" s="196"/>
+      <c r="AD25" s="197"/>
       <c r="AE25" s="22"/>
     </row>
-    <row r="26" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B26" s="132"/>
+    <row r="26" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B26" s="42"/>
       <c r="D26" s="20"/>
       <c r="E26" s="215"/>
       <c r="F26" s="216"/>
@@ -5495,18 +5495,18 @@
       <c r="T26" s="21"/>
       <c r="U26" s="21"/>
       <c r="V26" s="21"/>
-      <c r="W26" s="201"/>
-      <c r="X26" s="202"/>
+      <c r="W26" s="198"/>
+      <c r="X26" s="199"/>
       <c r="Y26" s="37"/>
-      <c r="Z26" s="201"/>
-      <c r="AA26" s="202"/>
+      <c r="Z26" s="198"/>
+      <c r="AA26" s="199"/>
       <c r="AB26" s="37"/>
-      <c r="AC26" s="201"/>
-      <c r="AD26" s="202"/>
+      <c r="AC26" s="198"/>
+      <c r="AD26" s="199"/>
       <c r="AE26" s="22"/>
     </row>
-    <row r="27" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B27" s="132"/>
+    <row r="27" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B27" s="42"/>
       <c r="D27" s="20"/>
       <c r="E27" s="218"/>
       <c r="F27" s="219"/>
@@ -5536,8 +5536,8 @@
       <c r="AD27" s="37"/>
       <c r="AE27" s="22"/>
     </row>
-    <row r="28" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B28" s="132"/>
+    <row r="28" spans="2:43" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B28" s="42"/>
       <c r="D28" s="20"/>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
@@ -5567,8 +5567,8 @@
       <c r="AD28" s="37"/>
       <c r="AE28" s="22"/>
     </row>
-    <row r="29" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="132"/>
+    <row r="29" spans="2:43" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="42"/>
       <c r="D29" s="20"/>
       <c r="E29" s="212" t="s">
         <v>24</v>
@@ -5595,19 +5595,23 @@
       <c r="W29" s="37"/>
       <c r="X29" s="37"/>
       <c r="Y29" s="37"/>
-      <c r="Z29" s="197" t="s">
+      <c r="Z29" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AA29" s="198"/>
+      <c r="AA29" s="195"/>
       <c r="AB29" s="37"/>
-      <c r="AC29" s="197" t="s">
+      <c r="AC29" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="AD29" s="198"/>
+      <c r="AD29" s="195"/>
       <c r="AE29" s="22"/>
-    </row>
-    <row r="30" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="132"/>
+      <c r="AQ29">
+        <f>250/2</f>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="2:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="42"/>
       <c r="D30" s="20"/>
       <c r="E30" s="215"/>
       <c r="F30" s="216"/>
@@ -5630,15 +5634,15 @@
       <c r="W30" s="37"/>
       <c r="X30" s="37"/>
       <c r="Y30" s="37"/>
-      <c r="Z30" s="199"/>
-      <c r="AA30" s="200"/>
+      <c r="Z30" s="196"/>
+      <c r="AA30" s="197"/>
       <c r="AB30" s="37"/>
-      <c r="AC30" s="199"/>
-      <c r="AD30" s="200"/>
+      <c r="AC30" s="196"/>
+      <c r="AD30" s="197"/>
       <c r="AE30" s="22"/>
     </row>
-    <row r="31" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="132"/>
+    <row r="31" spans="2:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="42"/>
       <c r="C31" s="13"/>
       <c r="D31" s="21"/>
       <c r="E31" s="215"/>
@@ -5662,15 +5666,15 @@
       <c r="W31" s="37"/>
       <c r="X31" s="37"/>
       <c r="Y31" s="37"/>
-      <c r="Z31" s="199"/>
-      <c r="AA31" s="200"/>
+      <c r="Z31" s="196"/>
+      <c r="AA31" s="197"/>
       <c r="AB31" s="37"/>
-      <c r="AC31" s="199"/>
-      <c r="AD31" s="200"/>
+      <c r="AC31" s="196"/>
+      <c r="AD31" s="197"/>
       <c r="AE31" s="22"/>
     </row>
-    <row r="32" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="132"/>
+    <row r="32" spans="2:43" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="42"/>
       <c r="D32" s="20"/>
       <c r="E32" s="215"/>
       <c r="F32" s="216"/>
@@ -5693,15 +5697,15 @@
       <c r="W32" s="37"/>
       <c r="X32" s="37"/>
       <c r="Y32" s="37"/>
-      <c r="Z32" s="199"/>
-      <c r="AA32" s="200"/>
+      <c r="Z32" s="196"/>
+      <c r="AA32" s="197"/>
       <c r="AB32" s="37"/>
-      <c r="AC32" s="199"/>
-      <c r="AD32" s="200"/>
+      <c r="AC32" s="196"/>
+      <c r="AD32" s="197"/>
       <c r="AE32" s="22"/>
     </row>
-    <row r="33" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="132"/>
+    <row r="33" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="42"/>
       <c r="D33" s="20"/>
       <c r="E33" s="215"/>
       <c r="F33" s="216"/>
@@ -5724,15 +5728,15 @@
       <c r="W33" s="37"/>
       <c r="X33" s="37"/>
       <c r="Y33" s="37"/>
-      <c r="Z33" s="199"/>
-      <c r="AA33" s="200"/>
+      <c r="Z33" s="196"/>
+      <c r="AA33" s="197"/>
       <c r="AB33" s="37"/>
-      <c r="AC33" s="199"/>
-      <c r="AD33" s="200"/>
+      <c r="AC33" s="196"/>
+      <c r="AD33" s="197"/>
       <c r="AE33" s="22"/>
     </row>
-    <row r="34" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="132"/>
+    <row r="34" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="42"/>
       <c r="D34" s="20"/>
       <c r="E34" s="215"/>
       <c r="F34" s="216"/>
@@ -5755,15 +5759,15 @@
       <c r="W34" s="37"/>
       <c r="X34" s="37"/>
       <c r="Y34" s="37"/>
-      <c r="Z34" s="199"/>
-      <c r="AA34" s="200"/>
+      <c r="Z34" s="196"/>
+      <c r="AA34" s="197"/>
       <c r="AB34" s="37"/>
-      <c r="AC34" s="199"/>
-      <c r="AD34" s="200"/>
+      <c r="AC34" s="196"/>
+      <c r="AD34" s="197"/>
       <c r="AE34" s="22"/>
     </row>
-    <row r="35" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="132"/>
+    <row r="35" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="42"/>
       <c r="D35" s="20"/>
       <c r="E35" s="218"/>
       <c r="F35" s="219"/>
@@ -5786,15 +5790,15 @@
       <c r="W35" s="37"/>
       <c r="X35" s="37"/>
       <c r="Y35" s="37"/>
-      <c r="Z35" s="201"/>
-      <c r="AA35" s="202"/>
+      <c r="Z35" s="198"/>
+      <c r="AA35" s="199"/>
       <c r="AB35" s="37"/>
-      <c r="AC35" s="201"/>
-      <c r="AD35" s="202"/>
+      <c r="AC35" s="198"/>
+      <c r="AD35" s="199"/>
       <c r="AE35" s="22"/>
     </row>
-    <row r="36" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B36" s="132"/>
+    <row r="36" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B36" s="42"/>
       <c r="D36" s="20"/>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
@@ -5824,8 +5828,8 @@
       <c r="AD36" s="21"/>
       <c r="AE36" s="22"/>
     </row>
-    <row r="37" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B37" s="132"/>
+    <row r="37" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B37" s="42"/>
       <c r="D37" s="20"/>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
@@ -5855,19 +5859,19 @@
       <c r="AD37" s="21"/>
       <c r="AE37" s="22"/>
     </row>
-    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="132"/>
+    <row r="38" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="42"/>
       <c r="D38" s="20"/>
       <c r="E38" s="37"/>
-      <c r="F38" s="250" t="s">
+      <c r="F38" s="221" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="251"/>
-      <c r="H38" s="256" t="s">
+      <c r="G38" s="222"/>
+      <c r="H38" s="227" t="s">
         <v>28</v>
       </c>
-      <c r="I38" s="257"/>
-      <c r="J38" s="258"/>
+      <c r="I38" s="228"/>
+      <c r="J38" s="229"/>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
@@ -5890,15 +5894,15 @@
       <c r="AD38" s="38"/>
       <c r="AE38" s="22"/>
     </row>
-    <row r="39" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B39" s="132"/>
+    <row r="39" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="42"/>
       <c r="D39" s="20"/>
       <c r="E39" s="37"/>
-      <c r="F39" s="252"/>
-      <c r="G39" s="253"/>
-      <c r="H39" s="259"/>
-      <c r="I39" s="260"/>
-      <c r="J39" s="261"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="224"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="232"/>
       <c r="K39" s="37"/>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
@@ -5909,150 +5913,150 @@
       <c r="R39" s="37"/>
       <c r="S39" s="37"/>
       <c r="T39" s="37"/>
-      <c r="U39" s="221" t="s">
+      <c r="U39" s="236" t="s">
         <v>41</v>
       </c>
-      <c r="V39" s="222"/>
-      <c r="W39" s="222"/>
-      <c r="X39" s="222"/>
-      <c r="Y39" s="222"/>
-      <c r="Z39" s="222"/>
-      <c r="AA39" s="223"/>
+      <c r="V39" s="237"/>
+      <c r="W39" s="237"/>
+      <c r="X39" s="237"/>
+      <c r="Y39" s="237"/>
+      <c r="Z39" s="237"/>
+      <c r="AA39" s="238"/>
       <c r="AB39" s="38"/>
       <c r="AC39" s="38"/>
       <c r="AD39" s="38"/>
       <c r="AE39" s="22"/>
     </row>
-    <row r="40" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B40" s="132"/>
+    <row r="40" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B40" s="42"/>
       <c r="D40" s="20"/>
       <c r="E40" s="37"/>
-      <c r="F40" s="254"/>
-      <c r="G40" s="255"/>
-      <c r="H40" s="259"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="261"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="232"/>
       <c r="K40" s="37"/>
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
-      <c r="N40" s="244" t="s">
+      <c r="N40" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="O40" s="245"/>
-      <c r="P40" s="245"/>
-      <c r="Q40" s="245"/>
-      <c r="R40" s="245"/>
-      <c r="S40" s="245"/>
-      <c r="T40" s="245"/>
-      <c r="U40" s="224"/>
-      <c r="V40" s="225"/>
-      <c r="W40" s="225"/>
-      <c r="X40" s="225"/>
-      <c r="Y40" s="225"/>
-      <c r="Z40" s="225"/>
-      <c r="AA40" s="226"/>
+      <c r="O40" s="207"/>
+      <c r="P40" s="207"/>
+      <c r="Q40" s="207"/>
+      <c r="R40" s="207"/>
+      <c r="S40" s="207"/>
+      <c r="T40" s="207"/>
+      <c r="U40" s="239"/>
+      <c r="V40" s="240"/>
+      <c r="W40" s="240"/>
+      <c r="X40" s="240"/>
+      <c r="Y40" s="240"/>
+      <c r="Z40" s="240"/>
+      <c r="AA40" s="241"/>
       <c r="AB40" s="38"/>
       <c r="AC40" s="38"/>
       <c r="AD40" s="38"/>
       <c r="AE40" s="22"/>
     </row>
-    <row r="41" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="132"/>
+    <row r="41" spans="2:31" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="42"/>
       <c r="D41" s="20"/>
       <c r="E41" s="37"/>
       <c r="F41" s="38"/>
       <c r="G41" s="38"/>
-      <c r="H41" s="259"/>
-      <c r="I41" s="260"/>
-      <c r="J41" s="261"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="232"/>
       <c r="K41" s="37"/>
       <c r="L41" s="37"/>
       <c r="M41" s="37"/>
-      <c r="N41" s="246"/>
-      <c r="O41" s="247"/>
-      <c r="P41" s="247"/>
-      <c r="Q41" s="247"/>
-      <c r="R41" s="247"/>
-      <c r="S41" s="247"/>
-      <c r="T41" s="247"/>
-      <c r="U41" s="224"/>
-      <c r="V41" s="225"/>
-      <c r="W41" s="225"/>
-      <c r="X41" s="225"/>
-      <c r="Y41" s="225"/>
-      <c r="Z41" s="225"/>
-      <c r="AA41" s="225"/>
-      <c r="AB41" s="229" t="s">
+      <c r="N41" s="208"/>
+      <c r="O41" s="209"/>
+      <c r="P41" s="209"/>
+      <c r="Q41" s="209"/>
+      <c r="R41" s="209"/>
+      <c r="S41" s="209"/>
+      <c r="T41" s="209"/>
+      <c r="U41" s="239"/>
+      <c r="V41" s="240"/>
+      <c r="W41" s="240"/>
+      <c r="X41" s="240"/>
+      <c r="Y41" s="240"/>
+      <c r="Z41" s="240"/>
+      <c r="AA41" s="240"/>
+      <c r="AB41" s="244" t="s">
         <v>30</v>
       </c>
-      <c r="AC41" s="230"/>
-      <c r="AD41" s="231"/>
+      <c r="AC41" s="245"/>
+      <c r="AD41" s="246"/>
       <c r="AE41" s="22"/>
     </row>
-    <row r="42" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B42" s="132"/>
+    <row r="42" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B42" s="42"/>
       <c r="D42" s="20"/>
       <c r="E42" s="37"/>
       <c r="F42" s="37"/>
       <c r="G42" s="39"/>
-      <c r="H42" s="259"/>
-      <c r="I42" s="260"/>
-      <c r="J42" s="261"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="232"/>
       <c r="K42" s="37"/>
       <c r="L42" s="37"/>
       <c r="M42" s="37"/>
-      <c r="N42" s="246"/>
-      <c r="O42" s="247"/>
-      <c r="P42" s="247"/>
-      <c r="Q42" s="247"/>
-      <c r="R42" s="247"/>
-      <c r="S42" s="247"/>
-      <c r="T42" s="247"/>
-      <c r="U42" s="224"/>
-      <c r="V42" s="225"/>
-      <c r="W42" s="225"/>
-      <c r="X42" s="225"/>
-      <c r="Y42" s="225"/>
-      <c r="Z42" s="225"/>
-      <c r="AA42" s="225"/>
-      <c r="AB42" s="232"/>
-      <c r="AC42" s="233"/>
-      <c r="AD42" s="234"/>
+      <c r="N42" s="208"/>
+      <c r="O42" s="209"/>
+      <c r="P42" s="209"/>
+      <c r="Q42" s="209"/>
+      <c r="R42" s="209"/>
+      <c r="S42" s="209"/>
+      <c r="T42" s="209"/>
+      <c r="U42" s="239"/>
+      <c r="V42" s="240"/>
+      <c r="W42" s="240"/>
+      <c r="X42" s="240"/>
+      <c r="Y42" s="240"/>
+      <c r="Z42" s="240"/>
+      <c r="AA42" s="240"/>
+      <c r="AB42" s="247"/>
+      <c r="AC42" s="248"/>
+      <c r="AD42" s="249"/>
       <c r="AE42" s="22"/>
     </row>
-    <row r="43" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B43" s="132"/>
+    <row r="43" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B43" s="42"/>
       <c r="D43" s="20"/>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
       <c r="G43" s="37"/>
-      <c r="H43" s="262"/>
-      <c r="I43" s="263"/>
-      <c r="J43" s="264"/>
+      <c r="H43" s="233"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="235"/>
       <c r="K43" s="37"/>
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
-      <c r="N43" s="246"/>
-      <c r="O43" s="247"/>
-      <c r="P43" s="247"/>
-      <c r="Q43" s="247"/>
-      <c r="R43" s="247"/>
-      <c r="S43" s="247"/>
-      <c r="T43" s="247"/>
-      <c r="U43" s="224"/>
-      <c r="V43" s="225"/>
-      <c r="W43" s="225"/>
-      <c r="X43" s="225"/>
-      <c r="Y43" s="225"/>
-      <c r="Z43" s="225"/>
-      <c r="AA43" s="225"/>
-      <c r="AB43" s="232"/>
-      <c r="AC43" s="233"/>
-      <c r="AD43" s="234"/>
+      <c r="N43" s="208"/>
+      <c r="O43" s="209"/>
+      <c r="P43" s="209"/>
+      <c r="Q43" s="209"/>
+      <c r="R43" s="209"/>
+      <c r="S43" s="209"/>
+      <c r="T43" s="209"/>
+      <c r="U43" s="239"/>
+      <c r="V43" s="240"/>
+      <c r="W43" s="240"/>
+      <c r="X43" s="240"/>
+      <c r="Y43" s="240"/>
+      <c r="Z43" s="240"/>
+      <c r="AA43" s="240"/>
+      <c r="AB43" s="247"/>
+      <c r="AC43" s="248"/>
+      <c r="AD43" s="249"/>
       <c r="AE43" s="22"/>
     </row>
-    <row r="44" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B44" s="132"/>
+    <row r="44" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B44" s="42"/>
       <c r="D44" s="20"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
@@ -6063,27 +6067,27 @@
       <c r="K44" s="37"/>
       <c r="L44" s="37"/>
       <c r="M44" s="37"/>
-      <c r="N44" s="246"/>
-      <c r="O44" s="247"/>
-      <c r="P44" s="247"/>
-      <c r="Q44" s="247"/>
-      <c r="R44" s="247"/>
-      <c r="S44" s="247"/>
-      <c r="T44" s="247"/>
-      <c r="U44" s="224"/>
-      <c r="V44" s="225"/>
-      <c r="W44" s="225"/>
-      <c r="X44" s="225"/>
-      <c r="Y44" s="225"/>
-      <c r="Z44" s="225"/>
-      <c r="AA44" s="225"/>
-      <c r="AB44" s="232"/>
-      <c r="AC44" s="233"/>
-      <c r="AD44" s="234"/>
+      <c r="N44" s="208"/>
+      <c r="O44" s="209"/>
+      <c r="P44" s="209"/>
+      <c r="Q44" s="209"/>
+      <c r="R44" s="209"/>
+      <c r="S44" s="209"/>
+      <c r="T44" s="209"/>
+      <c r="U44" s="239"/>
+      <c r="V44" s="240"/>
+      <c r="W44" s="240"/>
+      <c r="X44" s="240"/>
+      <c r="Y44" s="240"/>
+      <c r="Z44" s="240"/>
+      <c r="AA44" s="240"/>
+      <c r="AB44" s="247"/>
+      <c r="AC44" s="248"/>
+      <c r="AD44" s="249"/>
       <c r="AE44" s="22"/>
     </row>
-    <row r="45" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B45" s="132"/>
+    <row r="45" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B45" s="42"/>
       <c r="D45" s="20"/>
       <c r="E45" s="37"/>
       <c r="F45" s="37"/>
@@ -6094,35 +6098,35 @@
       <c r="K45" s="37"/>
       <c r="L45" s="37"/>
       <c r="M45" s="37"/>
-      <c r="N45" s="248"/>
-      <c r="O45" s="249"/>
-      <c r="P45" s="249"/>
-      <c r="Q45" s="249"/>
-      <c r="R45" s="249"/>
-      <c r="S45" s="249"/>
-      <c r="T45" s="249"/>
-      <c r="U45" s="227"/>
-      <c r="V45" s="228"/>
-      <c r="W45" s="228"/>
-      <c r="X45" s="228"/>
-      <c r="Y45" s="228"/>
-      <c r="Z45" s="228"/>
-      <c r="AA45" s="228"/>
-      <c r="AB45" s="235"/>
-      <c r="AC45" s="236"/>
-      <c r="AD45" s="237"/>
+      <c r="N45" s="210"/>
+      <c r="O45" s="211"/>
+      <c r="P45" s="211"/>
+      <c r="Q45" s="211"/>
+      <c r="R45" s="211"/>
+      <c r="S45" s="211"/>
+      <c r="T45" s="211"/>
+      <c r="U45" s="242"/>
+      <c r="V45" s="243"/>
+      <c r="W45" s="243"/>
+      <c r="X45" s="243"/>
+      <c r="Y45" s="243"/>
+      <c r="Z45" s="243"/>
+      <c r="AA45" s="243"/>
+      <c r="AB45" s="250"/>
+      <c r="AC45" s="251"/>
+      <c r="AD45" s="252"/>
       <c r="AE45" s="22"/>
     </row>
-    <row r="46" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B46" s="132"/>
+    <row r="46" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B46" s="42"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="238" t="s">
+      <c r="E46" s="200" t="s">
         <v>0</v>
       </c>
-      <c r="F46" s="239"/>
-      <c r="G46" s="239"/>
-      <c r="H46" s="239"/>
-      <c r="I46" s="240"/>
+      <c r="F46" s="201"/>
+      <c r="G46" s="201"/>
+      <c r="H46" s="201"/>
+      <c r="I46" s="202"/>
       <c r="J46" s="37"/>
       <c r="K46" s="37"/>
       <c r="L46" s="37"/>
@@ -6146,14 +6150,14 @@
       <c r="AD46" s="37"/>
       <c r="AE46" s="22"/>
     </row>
-    <row r="47" spans="2:31" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B47" s="133"/>
+    <row r="47" spans="2:31" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="B47" s="43"/>
       <c r="D47" s="23"/>
-      <c r="E47" s="241"/>
-      <c r="F47" s="242"/>
-      <c r="G47" s="242"/>
-      <c r="H47" s="242"/>
-      <c r="I47" s="243"/>
+      <c r="E47" s="203"/>
+      <c r="F47" s="204"/>
+      <c r="G47" s="204"/>
+      <c r="H47" s="204"/>
+      <c r="I47" s="205"/>
       <c r="J47" s="40"/>
       <c r="K47" s="40"/>
       <c r="L47" s="40"/>
@@ -6177,317 +6181,317 @@
       <c r="AD47" s="40"/>
       <c r="AE47" s="24"/>
     </row>
-    <row r="59" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA59" s="41" t="s">
+    <row r="59" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA59" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB59" s="41"/>
-      <c r="BC59" s="41"/>
-      <c r="BD59" s="41"/>
-      <c r="BE59" s="41"/>
-      <c r="BF59" s="41"/>
-      <c r="BG59" s="41"/>
-      <c r="BI59" s="41" t="s">
+      <c r="BB59" s="116"/>
+      <c r="BC59" s="116"/>
+      <c r="BD59" s="116"/>
+      <c r="BE59" s="116"/>
+      <c r="BF59" s="116"/>
+      <c r="BG59" s="116"/>
+      <c r="BI59" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BJ59" s="41"/>
-      <c r="BK59" s="41"/>
-      <c r="BL59" s="41"/>
-      <c r="BM59" s="41"/>
-      <c r="BN59" s="41"/>
-      <c r="BO59" s="41"/>
-    </row>
-    <row r="60" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA60" s="41"/>
-      <c r="BB60" s="41"/>
-      <c r="BC60" s="41"/>
-      <c r="BD60" s="41"/>
-      <c r="BE60" s="41"/>
-      <c r="BF60" s="41"/>
-      <c r="BG60" s="41"/>
-      <c r="BI60" s="41"/>
-      <c r="BJ60" s="41"/>
-      <c r="BK60" s="41"/>
-      <c r="BL60" s="41"/>
-      <c r="BM60" s="41"/>
-      <c r="BN60" s="41"/>
-      <c r="BO60" s="41"/>
-    </row>
-    <row r="61" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA61" s="41"/>
-      <c r="BB61" s="41"/>
-      <c r="BC61" s="41"/>
-      <c r="BD61" s="41"/>
-      <c r="BE61" s="41"/>
-      <c r="BF61" s="41"/>
-      <c r="BG61" s="41"/>
-      <c r="BI61" s="41"/>
-      <c r="BJ61" s="41"/>
-      <c r="BK61" s="41"/>
-      <c r="BL61" s="41"/>
-      <c r="BM61" s="41"/>
-      <c r="BN61" s="41"/>
-      <c r="BO61" s="41"/>
-    </row>
-    <row r="62" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA62" s="41"/>
-      <c r="BB62" s="41"/>
-      <c r="BC62" s="41"/>
-      <c r="BD62" s="41"/>
-      <c r="BE62" s="41"/>
-      <c r="BF62" s="41"/>
-      <c r="BG62" s="41"/>
-      <c r="BI62" s="41"/>
-      <c r="BJ62" s="41"/>
-      <c r="BK62" s="41"/>
-      <c r="BL62" s="41"/>
-      <c r="BM62" s="41"/>
-      <c r="BN62" s="41"/>
-      <c r="BO62" s="41"/>
-    </row>
-    <row r="63" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA63" s="41"/>
-      <c r="BB63" s="41"/>
-      <c r="BC63" s="41"/>
-      <c r="BD63" s="41"/>
-      <c r="BE63" s="41"/>
-      <c r="BF63" s="41"/>
-      <c r="BG63" s="41"/>
-      <c r="BI63" s="41"/>
-      <c r="BJ63" s="41"/>
-      <c r="BK63" s="41"/>
-      <c r="BL63" s="41"/>
-      <c r="BM63" s="41"/>
-      <c r="BN63" s="41"/>
-      <c r="BO63" s="41"/>
-    </row>
-    <row r="64" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA64" s="41"/>
-      <c r="BB64" s="41"/>
-      <c r="BC64" s="41"/>
-      <c r="BD64" s="41"/>
-      <c r="BE64" s="41"/>
-      <c r="BF64" s="41"/>
-      <c r="BG64" s="41"/>
-      <c r="BI64" s="41"/>
-      <c r="BJ64" s="41"/>
-      <c r="BK64" s="41"/>
-      <c r="BL64" s="41"/>
-      <c r="BM64" s="41"/>
-      <c r="BN64" s="41"/>
-      <c r="BO64" s="41"/>
-    </row>
-    <row r="66" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA66" s="41" t="s">
+      <c r="BJ59" s="116"/>
+      <c r="BK59" s="116"/>
+      <c r="BL59" s="116"/>
+      <c r="BM59" s="116"/>
+      <c r="BN59" s="116"/>
+      <c r="BO59" s="116"/>
+    </row>
+    <row r="60" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA60" s="116"/>
+      <c r="BB60" s="116"/>
+      <c r="BC60" s="116"/>
+      <c r="BD60" s="116"/>
+      <c r="BE60" s="116"/>
+      <c r="BF60" s="116"/>
+      <c r="BG60" s="116"/>
+      <c r="BI60" s="116"/>
+      <c r="BJ60" s="116"/>
+      <c r="BK60" s="116"/>
+      <c r="BL60" s="116"/>
+      <c r="BM60" s="116"/>
+      <c r="BN60" s="116"/>
+      <c r="BO60" s="116"/>
+    </row>
+    <row r="61" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA61" s="116"/>
+      <c r="BB61" s="116"/>
+      <c r="BC61" s="116"/>
+      <c r="BD61" s="116"/>
+      <c r="BE61" s="116"/>
+      <c r="BF61" s="116"/>
+      <c r="BG61" s="116"/>
+      <c r="BI61" s="116"/>
+      <c r="BJ61" s="116"/>
+      <c r="BK61" s="116"/>
+      <c r="BL61" s="116"/>
+      <c r="BM61" s="116"/>
+      <c r="BN61" s="116"/>
+      <c r="BO61" s="116"/>
+    </row>
+    <row r="62" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA62" s="116"/>
+      <c r="BB62" s="116"/>
+      <c r="BC62" s="116"/>
+      <c r="BD62" s="116"/>
+      <c r="BE62" s="116"/>
+      <c r="BF62" s="116"/>
+      <c r="BG62" s="116"/>
+      <c r="BI62" s="116"/>
+      <c r="BJ62" s="116"/>
+      <c r="BK62" s="116"/>
+      <c r="BL62" s="116"/>
+      <c r="BM62" s="116"/>
+      <c r="BN62" s="116"/>
+      <c r="BO62" s="116"/>
+    </row>
+    <row r="63" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA63" s="116"/>
+      <c r="BB63" s="116"/>
+      <c r="BC63" s="116"/>
+      <c r="BD63" s="116"/>
+      <c r="BE63" s="116"/>
+      <c r="BF63" s="116"/>
+      <c r="BG63" s="116"/>
+      <c r="BI63" s="116"/>
+      <c r="BJ63" s="116"/>
+      <c r="BK63" s="116"/>
+      <c r="BL63" s="116"/>
+      <c r="BM63" s="116"/>
+      <c r="BN63" s="116"/>
+      <c r="BO63" s="116"/>
+    </row>
+    <row r="64" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA64" s="116"/>
+      <c r="BB64" s="116"/>
+      <c r="BC64" s="116"/>
+      <c r="BD64" s="116"/>
+      <c r="BE64" s="116"/>
+      <c r="BF64" s="116"/>
+      <c r="BG64" s="116"/>
+      <c r="BI64" s="116"/>
+      <c r="BJ64" s="116"/>
+      <c r="BK64" s="116"/>
+      <c r="BL64" s="116"/>
+      <c r="BM64" s="116"/>
+      <c r="BN64" s="116"/>
+      <c r="BO64" s="116"/>
+    </row>
+    <row r="66" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA66" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB66" s="41"/>
-      <c r="BC66" s="41"/>
-      <c r="BD66" s="41"/>
-      <c r="BE66" s="41"/>
-      <c r="BF66" s="41"/>
-      <c r="BG66" s="41"/>
-      <c r="BI66" s="41" t="s">
+      <c r="BB66" s="116"/>
+      <c r="BC66" s="116"/>
+      <c r="BD66" s="116"/>
+      <c r="BE66" s="116"/>
+      <c r="BF66" s="116"/>
+      <c r="BG66" s="116"/>
+      <c r="BI66" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BJ66" s="41"/>
-      <c r="BK66" s="41"/>
-      <c r="BL66" s="41"/>
-      <c r="BM66" s="41"/>
-      <c r="BN66" s="41"/>
-      <c r="BO66" s="41"/>
-    </row>
-    <row r="67" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA67" s="41"/>
-      <c r="BB67" s="41"/>
-      <c r="BC67" s="41"/>
-      <c r="BD67" s="41"/>
-      <c r="BE67" s="41"/>
-      <c r="BF67" s="41"/>
-      <c r="BG67" s="41"/>
-      <c r="BI67" s="41"/>
-      <c r="BJ67" s="41"/>
-      <c r="BK67" s="41"/>
-      <c r="BL67" s="41"/>
-      <c r="BM67" s="41"/>
-      <c r="BN67" s="41"/>
-      <c r="BO67" s="41"/>
-    </row>
-    <row r="68" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA68" s="41"/>
-      <c r="BB68" s="41"/>
-      <c r="BC68" s="41"/>
-      <c r="BD68" s="41"/>
-      <c r="BE68" s="41"/>
-      <c r="BF68" s="41"/>
-      <c r="BG68" s="41"/>
-      <c r="BI68" s="41"/>
-      <c r="BJ68" s="41"/>
-      <c r="BK68" s="41"/>
-      <c r="BL68" s="41"/>
-      <c r="BM68" s="41"/>
-      <c r="BN68" s="41"/>
-      <c r="BO68" s="41"/>
-    </row>
-    <row r="69" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA69" s="41"/>
-      <c r="BB69" s="41"/>
-      <c r="BC69" s="41"/>
-      <c r="BD69" s="41"/>
-      <c r="BE69" s="41"/>
-      <c r="BF69" s="41"/>
-      <c r="BG69" s="41"/>
-      <c r="BI69" s="41"/>
-      <c r="BJ69" s="41"/>
-      <c r="BK69" s="41"/>
-      <c r="BL69" s="41"/>
-      <c r="BM69" s="41"/>
-      <c r="BN69" s="41"/>
-      <c r="BO69" s="41"/>
-    </row>
-    <row r="70" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA70" s="41"/>
-      <c r="BB70" s="41"/>
-      <c r="BC70" s="41"/>
-      <c r="BD70" s="41"/>
-      <c r="BE70" s="41"/>
-      <c r="BF70" s="41"/>
-      <c r="BG70" s="41"/>
-      <c r="BI70" s="41"/>
-      <c r="BJ70" s="41"/>
-      <c r="BK70" s="41"/>
-      <c r="BL70" s="41"/>
-      <c r="BM70" s="41"/>
-      <c r="BN70" s="41"/>
-      <c r="BO70" s="41"/>
-    </row>
-    <row r="71" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA71" s="41"/>
-      <c r="BB71" s="41"/>
-      <c r="BC71" s="41"/>
-      <c r="BD71" s="41"/>
-      <c r="BE71" s="41"/>
-      <c r="BF71" s="41"/>
-      <c r="BG71" s="41"/>
-      <c r="BI71" s="41"/>
-      <c r="BJ71" s="41"/>
-      <c r="BK71" s="41"/>
-      <c r="BL71" s="41"/>
-      <c r="BM71" s="41"/>
-      <c r="BN71" s="41"/>
-      <c r="BO71" s="41"/>
-    </row>
-    <row r="73" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA73" s="41" t="s">
+      <c r="BJ66" s="116"/>
+      <c r="BK66" s="116"/>
+      <c r="BL66" s="116"/>
+      <c r="BM66" s="116"/>
+      <c r="BN66" s="116"/>
+      <c r="BO66" s="116"/>
+    </row>
+    <row r="67" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA67" s="116"/>
+      <c r="BB67" s="116"/>
+      <c r="BC67" s="116"/>
+      <c r="BD67" s="116"/>
+      <c r="BE67" s="116"/>
+      <c r="BF67" s="116"/>
+      <c r="BG67" s="116"/>
+      <c r="BI67" s="116"/>
+      <c r="BJ67" s="116"/>
+      <c r="BK67" s="116"/>
+      <c r="BL67" s="116"/>
+      <c r="BM67" s="116"/>
+      <c r="BN67" s="116"/>
+      <c r="BO67" s="116"/>
+    </row>
+    <row r="68" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA68" s="116"/>
+      <c r="BB68" s="116"/>
+      <c r="BC68" s="116"/>
+      <c r="BD68" s="116"/>
+      <c r="BE68" s="116"/>
+      <c r="BF68" s="116"/>
+      <c r="BG68" s="116"/>
+      <c r="BI68" s="116"/>
+      <c r="BJ68" s="116"/>
+      <c r="BK68" s="116"/>
+      <c r="BL68" s="116"/>
+      <c r="BM68" s="116"/>
+      <c r="BN68" s="116"/>
+      <c r="BO68" s="116"/>
+    </row>
+    <row r="69" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA69" s="116"/>
+      <c r="BB69" s="116"/>
+      <c r="BC69" s="116"/>
+      <c r="BD69" s="116"/>
+      <c r="BE69" s="116"/>
+      <c r="BF69" s="116"/>
+      <c r="BG69" s="116"/>
+      <c r="BI69" s="116"/>
+      <c r="BJ69" s="116"/>
+      <c r="BK69" s="116"/>
+      <c r="BL69" s="116"/>
+      <c r="BM69" s="116"/>
+      <c r="BN69" s="116"/>
+      <c r="BO69" s="116"/>
+    </row>
+    <row r="70" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA70" s="116"/>
+      <c r="BB70" s="116"/>
+      <c r="BC70" s="116"/>
+      <c r="BD70" s="116"/>
+      <c r="BE70" s="116"/>
+      <c r="BF70" s="116"/>
+      <c r="BG70" s="116"/>
+      <c r="BI70" s="116"/>
+      <c r="BJ70" s="116"/>
+      <c r="BK70" s="116"/>
+      <c r="BL70" s="116"/>
+      <c r="BM70" s="116"/>
+      <c r="BN70" s="116"/>
+      <c r="BO70" s="116"/>
+    </row>
+    <row r="71" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA71" s="116"/>
+      <c r="BB71" s="116"/>
+      <c r="BC71" s="116"/>
+      <c r="BD71" s="116"/>
+      <c r="BE71" s="116"/>
+      <c r="BF71" s="116"/>
+      <c r="BG71" s="116"/>
+      <c r="BI71" s="116"/>
+      <c r="BJ71" s="116"/>
+      <c r="BK71" s="116"/>
+      <c r="BL71" s="116"/>
+      <c r="BM71" s="116"/>
+      <c r="BN71" s="116"/>
+      <c r="BO71" s="116"/>
+    </row>
+    <row r="73" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA73" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB73" s="41"/>
-      <c r="BC73" s="41"/>
-      <c r="BD73" s="41"/>
-      <c r="BE73" s="41"/>
-      <c r="BF73" s="41"/>
-      <c r="BG73" s="41"/>
-    </row>
-    <row r="74" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA74" s="41"/>
-      <c r="BB74" s="41"/>
-      <c r="BC74" s="41"/>
-      <c r="BD74" s="41"/>
-      <c r="BE74" s="41"/>
-      <c r="BF74" s="41"/>
-      <c r="BG74" s="41"/>
-    </row>
-    <row r="75" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA75" s="41"/>
-      <c r="BB75" s="41"/>
-      <c r="BC75" s="41"/>
-      <c r="BD75" s="41"/>
-      <c r="BE75" s="41"/>
-      <c r="BF75" s="41"/>
-      <c r="BG75" s="41"/>
-    </row>
-    <row r="76" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA76" s="41"/>
-      <c r="BB76" s="41"/>
-      <c r="BC76" s="41"/>
-      <c r="BD76" s="41"/>
-      <c r="BE76" s="41"/>
-      <c r="BF76" s="41"/>
-      <c r="BG76" s="41"/>
-    </row>
-    <row r="77" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA77" s="41"/>
-      <c r="BB77" s="41"/>
-      <c r="BC77" s="41"/>
-      <c r="BD77" s="41"/>
-      <c r="BE77" s="41"/>
-      <c r="BF77" s="41"/>
-      <c r="BG77" s="41"/>
-    </row>
-    <row r="78" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA78" s="41"/>
-      <c r="BB78" s="41"/>
-      <c r="BC78" s="41"/>
-      <c r="BD78" s="41"/>
-      <c r="BE78" s="41"/>
-      <c r="BF78" s="41"/>
-      <c r="BG78" s="41"/>
-    </row>
-    <row r="80" spans="53:67" x14ac:dyDescent="0.3">
-      <c r="BA80" s="41" t="s">
+      <c r="BB73" s="116"/>
+      <c r="BC73" s="116"/>
+      <c r="BD73" s="116"/>
+      <c r="BE73" s="116"/>
+      <c r="BF73" s="116"/>
+      <c r="BG73" s="116"/>
+    </row>
+    <row r="74" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA74" s="116"/>
+      <c r="BB74" s="116"/>
+      <c r="BC74" s="116"/>
+      <c r="BD74" s="116"/>
+      <c r="BE74" s="116"/>
+      <c r="BF74" s="116"/>
+      <c r="BG74" s="116"/>
+    </row>
+    <row r="75" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA75" s="116"/>
+      <c r="BB75" s="116"/>
+      <c r="BC75" s="116"/>
+      <c r="BD75" s="116"/>
+      <c r="BE75" s="116"/>
+      <c r="BF75" s="116"/>
+      <c r="BG75" s="116"/>
+    </row>
+    <row r="76" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA76" s="116"/>
+      <c r="BB76" s="116"/>
+      <c r="BC76" s="116"/>
+      <c r="BD76" s="116"/>
+      <c r="BE76" s="116"/>
+      <c r="BF76" s="116"/>
+      <c r="BG76" s="116"/>
+    </row>
+    <row r="77" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA77" s="116"/>
+      <c r="BB77" s="116"/>
+      <c r="BC77" s="116"/>
+      <c r="BD77" s="116"/>
+      <c r="BE77" s="116"/>
+      <c r="BF77" s="116"/>
+      <c r="BG77" s="116"/>
+    </row>
+    <row r="78" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA78" s="116"/>
+      <c r="BB78" s="116"/>
+      <c r="BC78" s="116"/>
+      <c r="BD78" s="116"/>
+      <c r="BE78" s="116"/>
+      <c r="BF78" s="116"/>
+      <c r="BG78" s="116"/>
+    </row>
+    <row r="80" spans="53:67" x14ac:dyDescent="0.25">
+      <c r="BA80" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="BB80" s="41"/>
-      <c r="BC80" s="41"/>
-      <c r="BD80" s="41"/>
-      <c r="BE80" s="41"/>
-      <c r="BF80" s="41"/>
-      <c r="BG80" s="41"/>
-    </row>
-    <row r="81" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA81" s="41"/>
-      <c r="BB81" s="41"/>
-      <c r="BC81" s="41"/>
-      <c r="BD81" s="41"/>
-      <c r="BE81" s="41"/>
-      <c r="BF81" s="41"/>
-      <c r="BG81" s="41"/>
-    </row>
-    <row r="82" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA82" s="41"/>
-      <c r="BB82" s="41"/>
-      <c r="BC82" s="41"/>
-      <c r="BD82" s="41"/>
-      <c r="BE82" s="41"/>
-      <c r="BF82" s="41"/>
-      <c r="BG82" s="41"/>
-    </row>
-    <row r="83" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA83" s="41"/>
-      <c r="BB83" s="41"/>
-      <c r="BC83" s="41"/>
-      <c r="BD83" s="41"/>
-      <c r="BE83" s="41"/>
-      <c r="BF83" s="41"/>
-      <c r="BG83" s="41"/>
-    </row>
-    <row r="84" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA84" s="41"/>
-      <c r="BB84" s="41"/>
-      <c r="BC84" s="41"/>
-      <c r="BD84" s="41"/>
-      <c r="BE84" s="41"/>
-      <c r="BF84" s="41"/>
-      <c r="BG84" s="41"/>
-    </row>
-    <row r="85" spans="53:68" x14ac:dyDescent="0.3">
-      <c r="BA85" s="41"/>
-      <c r="BB85" s="41"/>
-      <c r="BC85" s="41"/>
-      <c r="BD85" s="41"/>
-      <c r="BE85" s="41"/>
-      <c r="BF85" s="41"/>
-      <c r="BG85" s="41"/>
+      <c r="BB80" s="116"/>
+      <c r="BC80" s="116"/>
+      <c r="BD80" s="116"/>
+      <c r="BE80" s="116"/>
+      <c r="BF80" s="116"/>
+      <c r="BG80" s="116"/>
+    </row>
+    <row r="81" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA81" s="116"/>
+      <c r="BB81" s="116"/>
+      <c r="BC81" s="116"/>
+      <c r="BD81" s="116"/>
+      <c r="BE81" s="116"/>
+      <c r="BF81" s="116"/>
+      <c r="BG81" s="116"/>
+    </row>
+    <row r="82" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA82" s="116"/>
+      <c r="BB82" s="116"/>
+      <c r="BC82" s="116"/>
+      <c r="BD82" s="116"/>
+      <c r="BE82" s="116"/>
+      <c r="BF82" s="116"/>
+      <c r="BG82" s="116"/>
+    </row>
+    <row r="83" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA83" s="116"/>
+      <c r="BB83" s="116"/>
+      <c r="BC83" s="116"/>
+      <c r="BD83" s="116"/>
+      <c r="BE83" s="116"/>
+      <c r="BF83" s="116"/>
+      <c r="BG83" s="116"/>
+    </row>
+    <row r="84" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA84" s="116"/>
+      <c r="BB84" s="116"/>
+      <c r="BC84" s="116"/>
+      <c r="BD84" s="116"/>
+      <c r="BE84" s="116"/>
+      <c r="BF84" s="116"/>
+      <c r="BG84" s="116"/>
+    </row>
+    <row r="85" spans="53:68" x14ac:dyDescent="0.25">
+      <c r="BA85" s="116"/>
+      <c r="BB85" s="116"/>
+      <c r="BC85" s="116"/>
+      <c r="BD85" s="116"/>
+      <c r="BE85" s="116"/>
+      <c r="BF85" s="116"/>
+      <c r="BG85" s="116"/>
       <c r="BH85" s="15"/>
       <c r="BI85" s="15"/>
       <c r="BJ85" s="15"/>
@@ -6500,21 +6504,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="W20:X26"/>
-    <mergeCell ref="AC12:AD18"/>
-    <mergeCell ref="Z12:AA18"/>
-    <mergeCell ref="E46:I47"/>
-    <mergeCell ref="N40:T45"/>
-    <mergeCell ref="M21:S27"/>
-    <mergeCell ref="E29:K35"/>
-    <mergeCell ref="M29:S35"/>
-    <mergeCell ref="F38:G40"/>
-    <mergeCell ref="H38:J43"/>
-    <mergeCell ref="BI59:BO64"/>
-    <mergeCell ref="BA66:BG71"/>
-    <mergeCell ref="BI66:BO71"/>
-    <mergeCell ref="U39:AA45"/>
-    <mergeCell ref="AB41:AD45"/>
     <mergeCell ref="D2:AE2"/>
     <mergeCell ref="B4:B47"/>
     <mergeCell ref="BA73:BG78"/>
@@ -6531,6 +6520,21 @@
     <mergeCell ref="Z20:AA26"/>
     <mergeCell ref="AC20:AD26"/>
     <mergeCell ref="W12:X18"/>
+    <mergeCell ref="BI59:BO64"/>
+    <mergeCell ref="BA66:BG71"/>
+    <mergeCell ref="BI66:BO71"/>
+    <mergeCell ref="U39:AA45"/>
+    <mergeCell ref="AB41:AD45"/>
+    <mergeCell ref="W20:X26"/>
+    <mergeCell ref="AC12:AD18"/>
+    <mergeCell ref="Z12:AA18"/>
+    <mergeCell ref="E46:I47"/>
+    <mergeCell ref="N40:T45"/>
+    <mergeCell ref="M21:S27"/>
+    <mergeCell ref="E29:K35"/>
+    <mergeCell ref="M29:S35"/>
+    <mergeCell ref="F38:G40"/>
+    <mergeCell ref="H38:J43"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
